--- a/artfynd/A 26678-2026 artfynd.xlsx
+++ b/artfynd/A 26678-2026 artfynd.xlsx
@@ -2103,7 +2103,7 @@
         <v>136097908</v>
       </c>
       <c r="B15" t="n">
-        <v>96656</v>
+        <v>96659</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2220,7 +2220,7 @@
         <v>136097912</v>
       </c>
       <c r="B16" t="n">
-        <v>96656</v>
+        <v>96659</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2832,7 +2832,7 @@
         <v>136097911</v>
       </c>
       <c r="B22" t="n">
-        <v>96405</v>
+        <v>96408</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
         <v>136097914</v>
       </c>
       <c r="B27" t="n">
-        <v>96450</v>
+        <v>96453</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3663,7 +3663,7 @@
         <v>136097899</v>
       </c>
       <c r="B30" t="n">
-        <v>96677</v>
+        <v>96680</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3780,7 +3780,7 @@
         <v>136097906</v>
       </c>
       <c r="B31" t="n">
-        <v>96677</v>
+        <v>96680</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3897,7 +3897,7 @@
         <v>136097907</v>
       </c>
       <c r="B32" t="n">
-        <v>96677</v>
+        <v>96680</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4368,7 +4368,7 @@
         <v>136101564</v>
       </c>
       <c r="B36" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5672,7 +5672,7 @@
         <v>136097889</v>
       </c>
       <c r="B47" t="n">
-        <v>111636</v>
+        <v>111643</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5774,7 +5774,7 @@
         <v>136097891</v>
       </c>
       <c r="B48" t="n">
-        <v>111636</v>
+        <v>111643</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5876,7 +5876,7 @@
         <v>136097893</v>
       </c>
       <c r="B49" t="n">
-        <v>111636</v>
+        <v>111643</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5978,7 +5978,7 @@
         <v>136097900</v>
       </c>
       <c r="B50" t="n">
-        <v>111636</v>
+        <v>111643</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6080,7 +6080,7 @@
         <v>136097921</v>
       </c>
       <c r="B51" t="n">
-        <v>111636</v>
+        <v>111643</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6182,7 +6182,7 @@
         <v>136097933</v>
       </c>
       <c r="B52" t="n">
-        <v>111636</v>
+        <v>111643</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6284,7 +6284,7 @@
         <v>136097936</v>
       </c>
       <c r="B53" t="n">
-        <v>111636</v>
+        <v>111643</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6386,7 +6386,7 @@
         <v>136097939</v>
       </c>
       <c r="B54" t="n">
-        <v>111636</v>
+        <v>111643</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6488,7 +6488,7 @@
         <v>136097943</v>
       </c>
       <c r="B55" t="n">
-        <v>111636</v>
+        <v>111643</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6590,7 +6590,7 @@
         <v>136097946</v>
       </c>
       <c r="B56" t="n">
-        <v>111636</v>
+        <v>111643</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6799,7 +6799,7 @@
         <v>136097904</v>
       </c>
       <c r="B58" t="n">
-        <v>106483</v>
+        <v>106486</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         <v>136097886</v>
       </c>
       <c r="B59" t="n">
-        <v>102468</v>
+        <v>102471</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7003,7 +7003,7 @@
         <v>136097892</v>
       </c>
       <c r="B60" t="n">
-        <v>102468</v>
+        <v>102471</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7105,7 +7105,7 @@
         <v>136097894</v>
       </c>
       <c r="B61" t="n">
-        <v>102468</v>
+        <v>102471</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7207,7 +7207,7 @@
         <v>136097901</v>
       </c>
       <c r="B62" t="n">
-        <v>102468</v>
+        <v>102471</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7309,7 +7309,7 @@
         <v>136097903</v>
       </c>
       <c r="B63" t="n">
-        <v>102468</v>
+        <v>102471</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7411,7 +7411,7 @@
         <v>136097913</v>
       </c>
       <c r="B64" t="n">
-        <v>102468</v>
+        <v>102471</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7513,7 +7513,7 @@
         <v>136097916</v>
       </c>
       <c r="B65" t="n">
-        <v>102468</v>
+        <v>102471</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7615,7 +7615,7 @@
         <v>136098084</v>
       </c>
       <c r="B66" t="n">
-        <v>102468</v>
+        <v>102471</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7717,7 +7717,7 @@
         <v>136097902</v>
       </c>
       <c r="B67" t="n">
-        <v>104352</v>
+        <v>104355</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8242,7 +8242,7 @@
         <v>136097895</v>
       </c>
       <c r="B72" t="n">
-        <v>101552</v>
+        <v>101555</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8344,7 +8344,7 @@
         <v>136097917</v>
       </c>
       <c r="B73" t="n">
-        <v>101552</v>
+        <v>101555</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8446,7 +8446,7 @@
         <v>136097919</v>
       </c>
       <c r="B74" t="n">
-        <v>101552</v>
+        <v>101555</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8548,7 +8548,7 @@
         <v>136097920</v>
       </c>
       <c r="B75" t="n">
-        <v>101552</v>
+        <v>101555</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8650,7 +8650,7 @@
         <v>136097940</v>
       </c>
       <c r="B76" t="n">
-        <v>101552</v>
+        <v>101555</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8752,7 +8752,7 @@
         <v>136097945</v>
       </c>
       <c r="B77" t="n">
-        <v>101552</v>
+        <v>101555</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8854,7 +8854,7 @@
         <v>136097888</v>
       </c>
       <c r="B78" t="n">
-        <v>101454</v>
+        <v>101457</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8956,7 +8956,7 @@
         <v>136097935</v>
       </c>
       <c r="B79" t="n">
-        <v>101454</v>
+        <v>101457</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9058,7 +9058,7 @@
         <v>136097937</v>
       </c>
       <c r="B80" t="n">
-        <v>101454</v>
+        <v>101457</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>

--- a/artfynd/A 26678-2026 artfynd.xlsx
+++ b/artfynd/A 26678-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ82"/>
+  <dimension ref="A1:AZ86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2103,7 +2103,7 @@
         <v>136097908</v>
       </c>
       <c r="B15" t="n">
-        <v>96659</v>
+        <v>96660</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2220,7 +2220,7 @@
         <v>136097912</v>
       </c>
       <c r="B16" t="n">
-        <v>96659</v>
+        <v>96660</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2319,10 +2319,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132445997</v>
+        <v>136707418</v>
       </c>
       <c r="B17" t="n">
-        <v>96501</v>
+        <v>96660</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2330,34 +2330,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2671</v>
+        <v>2667</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Janses kulle, Dls</t>
+          <t>Väster om Rannebergets NR, Dls</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>348634</v>
+        <v>348521</v>
       </c>
       <c r="R17" t="n">
-        <v>6519450</v>
+        <v>6519371</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2384,12 +2384,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2415,13 +2415,13 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132445997</t>
+          <t>https://artportalen.se/Sighting/136707418</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132446001</v>
+        <v>132445997</v>
       </c>
       <c r="B18" t="n">
         <v>96501</v>
@@ -2456,10 +2456,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>348660</v>
+        <v>348634</v>
       </c>
       <c r="R18" t="n">
-        <v>6519418</v>
+        <v>6519450</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2517,13 +2517,13 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132446001</t>
+          <t>https://artportalen.se/Sighting/132445997</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132446003</v>
+        <v>132446001</v>
       </c>
       <c r="B19" t="n">
         <v>96501</v>
@@ -2558,10 +2558,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>348643</v>
+        <v>348660</v>
       </c>
       <c r="R19" t="n">
-        <v>6519393</v>
+        <v>6519418</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2619,13 +2619,13 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132446003</t>
+          <t>https://artportalen.se/Sighting/132446001</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132446018</v>
+        <v>132446003</v>
       </c>
       <c r="B20" t="n">
         <v>96501</v>
@@ -2660,10 +2660,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>348663</v>
+        <v>348643</v>
       </c>
       <c r="R20" t="n">
-        <v>6519352</v>
+        <v>6519393</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2721,13 +2721,13 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132446018</t>
+          <t>https://artportalen.se/Sighting/132446003</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132446031</v>
+        <v>132446018</v>
       </c>
       <c r="B21" t="n">
         <v>96501</v>
@@ -2758,14 +2758,14 @@
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Skårdalens gamla tomt, Dls</t>
+          <t>Janses kulle, Dls</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>348743</v>
+        <v>348663</v>
       </c>
       <c r="R21" t="n">
-        <v>6519161</v>
+        <v>6519352</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2823,16 +2823,16 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132446031</t>
+          <t>https://artportalen.se/Sighting/132446018</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>136097911</v>
+        <v>132446031</v>
       </c>
       <c r="B22" t="n">
-        <v>96408</v>
+        <v>96501</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2840,34 +2840,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2676</v>
+        <v>2671</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Grov baronmossa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Anomodon viticulosus</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hedw.) Hook. &amp; Taylor</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Väst om Rannebergets naturreservat, Dls</t>
+          <t>Skårdalens gamla tomt, Dls</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>348538</v>
+        <v>348743</v>
       </c>
       <c r="R22" t="n">
-        <v>6519538</v>
+        <v>6519161</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2925,16 +2925,16 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136097911</t>
+          <t>https://artportalen.se/Sighting/132446031</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132446004</v>
+        <v>136707412</v>
       </c>
       <c r="B23" t="n">
-        <v>96306</v>
+        <v>96649</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2942,34 +2942,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2779</v>
+        <v>2671</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Janses kulle, Dls</t>
+          <t>Väster om Rannebergets NR, Dls</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>348632</v>
+        <v>348775</v>
       </c>
       <c r="R23" t="n">
-        <v>6519384</v>
+        <v>6519594</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -2996,12 +2996,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3027,16 +3027,16 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132446004</t>
+          <t>https://artportalen.se/Sighting/136707412</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132446012</v>
+        <v>136097911</v>
       </c>
       <c r="B24" t="n">
-        <v>96306</v>
+        <v>96409</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3044,34 +3044,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2779</v>
+        <v>2676</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Grov baronmossa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Anomodon viticulosus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Hedw.) Hook. &amp; Taylor</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Janses kulle, Dls</t>
+          <t>Väst om Rannebergets naturreservat, Dls</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>348647</v>
+        <v>348538</v>
       </c>
       <c r="R24" t="n">
-        <v>6519347</v>
+        <v>6519538</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3098,12 +3098,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3129,13 +3129,13 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132446012</t>
+          <t>https://artportalen.se/Sighting/136097911</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132446017</v>
+        <v>132446004</v>
       </c>
       <c r="B25" t="n">
         <v>96306</v>
@@ -3170,10 +3170,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>348663</v>
+        <v>348632</v>
       </c>
       <c r="R25" t="n">
-        <v>6519352</v>
+        <v>6519384</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3231,13 +3231,13 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132446017</t>
+          <t>https://artportalen.se/Sighting/132446004</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132446022</v>
+        <v>132446012</v>
       </c>
       <c r="B26" t="n">
         <v>96306</v>
@@ -3268,14 +3268,14 @@
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Skårdalens gamla tomt, Dls</t>
+          <t>Janses kulle, Dls</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>348678</v>
+        <v>348647</v>
       </c>
       <c r="R26" t="n">
-        <v>6519308</v>
+        <v>6519347</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3333,16 +3333,16 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132446022</t>
+          <t>https://artportalen.se/Sighting/132446012</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>136097914</v>
+        <v>132446017</v>
       </c>
       <c r="B27" t="n">
-        <v>96453</v>
+        <v>96306</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3370,14 +3370,14 @@
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Väst om Rannebergets naturreservat, Dls</t>
+          <t>Janses kulle, Dls</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>348537</v>
+        <v>348663</v>
       </c>
       <c r="R27" t="n">
-        <v>6519535</v>
+        <v>6519352</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3404,12 +3404,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3435,16 +3435,16 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136097914</t>
+          <t>https://artportalen.se/Sighting/132446017</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132446011</v>
+        <v>132446022</v>
       </c>
       <c r="B28" t="n">
-        <v>96533</v>
+        <v>96306</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3452,34 +3452,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2818</v>
+        <v>2779</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Janses kulle, Dls</t>
+          <t>Skårdalens gamla tomt, Dls</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>348654</v>
+        <v>348678</v>
       </c>
       <c r="R28" t="n">
-        <v>6519348</v>
+        <v>6519308</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3537,16 +3537,16 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132446011</t>
+          <t>https://artportalen.se/Sighting/132446022</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132446019</v>
+        <v>136097914</v>
       </c>
       <c r="B29" t="n">
-        <v>96533</v>
+        <v>96454</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3554,34 +3554,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2818</v>
+        <v>2779</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Janses kulle, Dls</t>
+          <t>Väst om Rannebergets naturreservat, Dls</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>348662</v>
+        <v>348537</v>
       </c>
       <c r="R29" t="n">
-        <v>6519330</v>
+        <v>6519535</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3624,21 +3624,6 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
@@ -3654,16 +3639,16 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132446019</t>
+          <t>https://artportalen.se/Sighting/136097914</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>136097899</v>
+        <v>132446011</v>
       </c>
       <c r="B30" t="n">
-        <v>96680</v>
+        <v>96533</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3691,14 +3676,14 @@
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Väst om Rannebergets naturreservat, Dls</t>
+          <t>Janses kulle, Dls</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>348719</v>
+        <v>348654</v>
       </c>
       <c r="R30" t="n">
-        <v>6519093</v>
+        <v>6519348</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3725,12 +3710,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3741,21 +3726,6 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
@@ -3771,16 +3741,16 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136097899</t>
+          <t>https://artportalen.se/Sighting/132446011</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>136097906</v>
+        <v>132446019</v>
       </c>
       <c r="B31" t="n">
-        <v>96680</v>
+        <v>96533</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3808,14 +3778,14 @@
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Väst om Rannebergets naturreservat, Dls</t>
+          <t>Janses kulle, Dls</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>348560</v>
+        <v>348662</v>
       </c>
       <c r="R31" t="n">
-        <v>6519339</v>
+        <v>6519330</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3842,12 +3812,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3888,16 +3858,16 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136097906</t>
+          <t>https://artportalen.se/Sighting/132446019</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>136097907</v>
+        <v>136097899</v>
       </c>
       <c r="B32" t="n">
-        <v>96680</v>
+        <v>96681</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3929,10 +3899,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>348545</v>
+        <v>348719</v>
       </c>
       <c r="R32" t="n">
-        <v>6519374</v>
+        <v>6519093</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4005,16 +3975,16 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136097907</t>
+          <t>https://artportalen.se/Sighting/136097899</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132446025</v>
+        <v>136097906</v>
       </c>
       <c r="B33" t="n">
-        <v>92031</v>
+        <v>96681</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4022,34 +3992,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5321</v>
+        <v>2818</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Skårdalens gamla tomt, Dls</t>
+          <t>Väst om Rannebergets naturreservat, Dls</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>348701</v>
+        <v>348560</v>
       </c>
       <c r="R33" t="n">
-        <v>6519282</v>
+        <v>6519339</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4076,12 +4046,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4090,23 +4060,22 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4123,16 +4092,16 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132446025</t>
+          <t>https://artportalen.se/Sighting/136097906</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132446026</v>
+        <v>136097907</v>
       </c>
       <c r="B34" t="n">
-        <v>92031</v>
+        <v>96681</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4140,34 +4109,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5321</v>
+        <v>2818</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Skårdalens gamla tomt, Dls</t>
+          <t>Väst om Rannebergets naturreservat, Dls</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>348708</v>
+        <v>348545</v>
       </c>
       <c r="R34" t="n">
-        <v>6519267</v>
+        <v>6519374</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4194,12 +4163,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4208,23 +4177,22 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4241,13 +4209,13 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132446026</t>
+          <t>https://artportalen.se/Sighting/136097907</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132446028</v>
+        <v>132446025</v>
       </c>
       <c r="B35" t="n">
         <v>92031</v>
@@ -4282,10 +4250,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>348666</v>
+        <v>348701</v>
       </c>
       <c r="R35" t="n">
-        <v>6519254</v>
+        <v>6519282</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4359,16 +4327,16 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132446028</t>
+          <t>https://artportalen.se/Sighting/132446025</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>136101564</v>
+        <v>132446026</v>
       </c>
       <c r="B36" t="n">
-        <v>92162</v>
+        <v>92031</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4396,14 +4364,14 @@
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Väst om Ranneberget, Dls</t>
+          <t>Skårdalens gamla tomt, Dls</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>348774</v>
+        <v>348708</v>
       </c>
       <c r="R36" t="n">
-        <v>6519585</v>
+        <v>6519267</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4430,12 +4398,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4477,16 +4445,16 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136101564</t>
+          <t>https://artportalen.se/Sighting/132446026</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132446023</v>
+        <v>132446028</v>
       </c>
       <c r="B37" t="n">
-        <v>4776</v>
+        <v>92031</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4494,39 +4462,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100299</v>
+        <v>5321</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Skårdalens gamla tomt, Dls</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>348665</v>
+        <v>348666</v>
       </c>
       <c r="R37" t="n">
-        <v>6519298</v>
+        <v>6519254</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4567,22 +4530,23 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -4599,16 +4563,16 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132446023</t>
+          <t>https://artportalen.se/Sighting/132446028</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132446079</v>
+        <v>136101564</v>
       </c>
       <c r="B38" t="n">
-        <v>4776</v>
+        <v>92163</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4616,39 +4580,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100299</v>
+        <v>5321</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Barrskogen mellan Lilla Skårsdalstjärnet och Kvarntjärnet, Dls</t>
+          <t>Väst om Ranneberget, Dls</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>348740</v>
+        <v>348774</v>
       </c>
       <c r="R38" t="n">
-        <v>6519761</v>
+        <v>6519585</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4675,12 +4634,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4689,22 +4648,23 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK38" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -4721,16 +4681,16 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132446079</t>
+          <t>https://artportalen.se/Sighting/136101564</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132446074</v>
+        <v>132446023</v>
       </c>
       <c r="B39" t="n">
-        <v>5181</v>
+        <v>4776</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4738,39 +4698,39 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100526</v>
+        <v>100299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Barrskogen mellan Lilla Skårsdalstjärnet och Kvarntjärnet, Dls</t>
+          <t>Skårdalens gamla tomt, Dls</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>348747</v>
+        <v>348665</v>
       </c>
       <c r="R39" t="n">
-        <v>6519747</v>
+        <v>6519298</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4811,7 +4771,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4844,16 +4803,16 @@
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132446074</t>
+          <t>https://artportalen.se/Sighting/132446023</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>136097897</v>
+        <v>132446079</v>
       </c>
       <c r="B40" t="n">
-        <v>5182</v>
+        <v>4776</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4861,21 +4820,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100526</v>
+        <v>100299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4886,14 +4845,14 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Väst om Rannebergets naturreservat, Dls</t>
+          <t>Barrskogen mellan Lilla Skårsdalstjärnet och Kvarntjärnet, Dls</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>348723</v>
+        <v>348740</v>
       </c>
       <c r="R40" t="n">
-        <v>6519121</v>
+        <v>6519761</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4920,12 +4879,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4966,16 +4925,16 @@
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136097897</t>
+          <t>https://artportalen.se/Sighting/132446079</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>136097898</v>
+        <v>132446074</v>
       </c>
       <c r="B41" t="n">
-        <v>5202</v>
+        <v>5181</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4983,39 +4942,39 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>105930</v>
+        <v>100526</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Väst om Rannebergets naturreservat, Dls</t>
+          <t>Barrskogen mellan Lilla Skårsdalstjärnet och Kvarntjärnet, Dls</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>348723</v>
+        <v>348747</v>
       </c>
       <c r="R41" t="n">
-        <v>6519121</v>
+        <v>6519747</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5042,12 +5001,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5056,6 +5015,7 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -5088,16 +5048,16 @@
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136097898</t>
+          <t>https://artportalen.se/Sighting/132446074</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>136097942</v>
+        <v>136097897</v>
       </c>
       <c r="B42" t="n">
-        <v>5202</v>
+        <v>5182</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5105,21 +5065,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>105930</v>
+        <v>100526</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5134,10 +5094,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>348780</v>
+        <v>348723</v>
       </c>
       <c r="R42" t="n">
-        <v>6519577</v>
+        <v>6519121</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5210,38 +5170,38 @@
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136097942</t>
+          <t>https://artportalen.se/Sighting/136097897</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132445999</v>
+        <v>136097898</v>
       </c>
       <c r="B43" t="n">
-        <v>8374</v>
+        <v>5202</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>106540</v>
+        <v>105930</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Svart askbastborre</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hylesinus crenatus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fabricius, 1787)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5252,14 +5212,14 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Janses kulle, Dls</t>
+          <t>Väst om Rannebergets naturreservat, Dls</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>348665</v>
+        <v>348723</v>
       </c>
       <c r="R43" t="n">
-        <v>6519431</v>
+        <v>6519121</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5286,12 +5246,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5305,17 +5265,17 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>ask</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -5332,38 +5292,38 @@
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132445999</t>
+          <t>https://artportalen.se/Sighting/136097898</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132446029</v>
+        <v>136097942</v>
       </c>
       <c r="B44" t="n">
-        <v>8374</v>
+        <v>5202</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>106540</v>
+        <v>105930</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Svart askbastborre</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hylesinus crenatus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fabricius, 1787)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5374,14 +5334,14 @@
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Skårdalens gamla tomt, Dls</t>
+          <t>Väst om Rannebergets naturreservat, Dls</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>348623</v>
+        <v>348780</v>
       </c>
       <c r="R44" t="n">
-        <v>6519241</v>
+        <v>6519577</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5408,12 +5368,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5427,17 +5387,17 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>ask</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK44" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -5454,51 +5414,56 @@
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132446029</t>
+          <t>https://artportalen.se/Sighting/136097942</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>132446075</v>
+        <v>132445999</v>
       </c>
       <c r="B45" t="n">
-        <v>8449</v>
+        <v>8374</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>106554</v>
+        <v>106540</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Svart askbastborre</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Hylesinus crenatus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Fabricius, 1787)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Barrskogen mellan Lilla Skårsdalstjärnet och Kvarntjärnet, Dls</t>
+          <t>Janses kulle, Dls</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>348741</v>
+        <v>348665</v>
       </c>
       <c r="R45" t="n">
-        <v>6519743</v>
+        <v>6519431</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5542,6 +5507,21 @@
       <c r="AG45" t="b">
         <v>0</v>
       </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
@@ -5556,38 +5536,38 @@
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132446075</t>
+          <t>https://artportalen.se/Sighting/132445999</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>136097896</v>
+        <v>132446029</v>
       </c>
       <c r="B46" t="n">
-        <v>8452</v>
+        <v>8374</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>106554</v>
+        <v>106540</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Svart askbastborre</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Hylesinus crenatus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Fabricius, 1787)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5598,14 +5578,14 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Väst om Rannebergets naturreservat, Dls</t>
+          <t>Skårdalens gamla tomt, Dls</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>348699</v>
+        <v>348623</v>
       </c>
       <c r="R46" t="n">
-        <v>6519187</v>
+        <v>6519241</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5632,12 +5612,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5648,6 +5628,21 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
@@ -5663,51 +5658,51 @@
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136097896</t>
+          <t>https://artportalen.se/Sighting/132446029</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>136097889</v>
+        <v>132446075</v>
       </c>
       <c r="B47" t="n">
-        <v>111643</v>
+        <v>8449</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>219711</v>
+        <v>106554</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Väst om Rannebergets naturreservat, Dls</t>
+          <t>Barrskogen mellan Lilla Skårsdalstjärnet och Kvarntjärnet, Dls</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>348824</v>
+        <v>348741</v>
       </c>
       <c r="R47" t="n">
-        <v>6519586</v>
+        <v>6519743</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5734,12 +5729,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5765,51 +5760,56 @@
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136097889</t>
+          <t>https://artportalen.se/Sighting/132446075</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>136097891</v>
+        <v>136097896</v>
       </c>
       <c r="B48" t="n">
-        <v>111643</v>
+        <v>8452</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>219711</v>
+        <v>106554</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Väst om Rannebergets naturreservat, Dls</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>348614</v>
+        <v>348699</v>
       </c>
       <c r="R48" t="n">
-        <v>6519482</v>
+        <v>6519187</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5867,33 +5867,33 @@
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136097891</t>
+          <t>https://artportalen.se/Sighting/136097896</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>136097893</v>
+        <v>136707427</v>
       </c>
       <c r="B49" t="n">
-        <v>111643</v>
+        <v>107856</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>219711</v>
+        <v>219686</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Vätteros</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Lathraea squamaria</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -5904,14 +5904,14 @@
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Väst om Rannebergets naturreservat, Dls</t>
+          <t>Väster om Rannebergets NR, Dls</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>348612</v>
+        <v>348620</v>
       </c>
       <c r="R49" t="n">
-        <v>6519392</v>
+        <v>6519302</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5938,12 +5938,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5969,16 +5969,16 @@
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136097893</t>
+          <t>https://artportalen.se/Sighting/136707427</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>136097900</v>
+        <v>136097889</v>
       </c>
       <c r="B50" t="n">
-        <v>111643</v>
+        <v>111644</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6010,10 +6010,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>348618</v>
+        <v>348824</v>
       </c>
       <c r="R50" t="n">
-        <v>6519260</v>
+        <v>6519586</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6071,16 +6071,16 @@
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136097900</t>
+          <t>https://artportalen.se/Sighting/136097889</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>136097921</v>
+        <v>136097891</v>
       </c>
       <c r="B51" t="n">
-        <v>111643</v>
+        <v>111644</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6112,10 +6112,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>348587</v>
+        <v>348614</v>
       </c>
       <c r="R51" t="n">
-        <v>6519511</v>
+        <v>6519482</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6173,16 +6173,16 @@
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136097921</t>
+          <t>https://artportalen.se/Sighting/136097891</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>136097933</v>
+        <v>136097893</v>
       </c>
       <c r="B52" t="n">
-        <v>111643</v>
+        <v>111644</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6214,10 +6214,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>348673</v>
+        <v>348612</v>
       </c>
       <c r="R52" t="n">
-        <v>6519697</v>
+        <v>6519392</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6275,16 +6275,16 @@
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136097933</t>
+          <t>https://artportalen.se/Sighting/136097893</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>136097936</v>
+        <v>136097900</v>
       </c>
       <c r="B53" t="n">
-        <v>111643</v>
+        <v>111644</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6316,10 +6316,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>348711</v>
+        <v>348618</v>
       </c>
       <c r="R53" t="n">
-        <v>6519665</v>
+        <v>6519260</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6377,16 +6377,16 @@
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136097936</t>
+          <t>https://artportalen.se/Sighting/136097900</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>136097939</v>
+        <v>136097921</v>
       </c>
       <c r="B54" t="n">
-        <v>111643</v>
+        <v>111644</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6418,10 +6418,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>348745</v>
+        <v>348587</v>
       </c>
       <c r="R54" t="n">
-        <v>6519603</v>
+        <v>6519511</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6479,16 +6479,16 @@
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136097939</t>
+          <t>https://artportalen.se/Sighting/136097921</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>136097943</v>
+        <v>136097933</v>
       </c>
       <c r="B55" t="n">
-        <v>111643</v>
+        <v>111644</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6520,10 +6520,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>348818</v>
+        <v>348673</v>
       </c>
       <c r="R55" t="n">
-        <v>6519588</v>
+        <v>6519697</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6581,16 +6581,16 @@
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136097943</t>
+          <t>https://artportalen.se/Sighting/136097933</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>136097946</v>
+        <v>136097936</v>
       </c>
       <c r="B56" t="n">
-        <v>111643</v>
+        <v>111644</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6622,10 +6622,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>348846</v>
+        <v>348711</v>
       </c>
       <c r="R56" t="n">
-        <v>6519619</v>
+        <v>6519665</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6683,16 +6683,16 @@
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136097946</t>
+          <t>https://artportalen.se/Sighting/136097936</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>132335133</v>
+        <v>136097939</v>
       </c>
       <c r="B57" t="n">
-        <v>101974</v>
+        <v>111644</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6700,16 +6700,16 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220075</v>
+        <v>219711</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Gullpudra</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Chrysosplenium alternifolium</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -6720,17 +6720,17 @@
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Vandringstjärnet, ca 160 m NO om tjärnets norra ände, Dls</t>
+          <t>Väst om Rannebergets naturreservat, Dls</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>348563</v>
+        <v>348745</v>
       </c>
       <c r="R57" t="n">
-        <v>6519443</v>
+        <v>6519603</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6754,12 +6754,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6770,58 +6770,53 @@
       </c>
       <c r="AG57" t="b">
         <v>0</v>
-      </c>
-      <c r="AI57" t="inlineStr">
-        <is>
-          <t>Sumpskog med klibbal.</t>
-        </is>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Leif Appelgren</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Leif Appelgren</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132335133</t>
+          <t>https://artportalen.se/Sighting/136097939</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>136097904</v>
+        <v>136097943</v>
       </c>
       <c r="B58" t="n">
-        <v>106486</v>
+        <v>111644</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>221144</v>
+        <v>219711</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6831,10 +6826,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>348602</v>
+        <v>348818</v>
       </c>
       <c r="R58" t="n">
-        <v>6519311</v>
+        <v>6519588</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6892,16 +6887,16 @@
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136097904</t>
+          <t>https://artportalen.se/Sighting/136097943</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>136097886</v>
+        <v>136097946</v>
       </c>
       <c r="B59" t="n">
-        <v>102471</v>
+        <v>111644</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6909,21 +6904,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>221235</v>
+        <v>219711</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6933,10 +6928,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>348812</v>
+        <v>348846</v>
       </c>
       <c r="R59" t="n">
-        <v>6519662</v>
+        <v>6519619</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -6994,16 +6989,16 @@
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136097886</t>
+          <t>https://artportalen.se/Sighting/136097946</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>136097892</v>
+        <v>132335133</v>
       </c>
       <c r="B60" t="n">
-        <v>102471</v>
+        <v>101974</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7011,37 +7006,37 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>221235</v>
+        <v>220075</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Gullpudra</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Chrysosplenium alternifolium</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Väst om Rannebergets naturreservat, Dls</t>
+          <t>Vandringstjärnet, ca 160 m NO om tjärnets norra ände, Dls</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>348607</v>
+        <v>348563</v>
       </c>
       <c r="R60" t="n">
-        <v>6519437</v>
+        <v>6519443</v>
       </c>
       <c r="S60" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7065,12 +7060,12 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7081,66 +7076,71 @@
       </c>
       <c r="AG60" t="b">
         <v>0</v>
+      </c>
+      <c r="AI60" t="inlineStr">
+        <is>
+          <t>Sumpskog med klibbal.</t>
+        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Leif Appelgren</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Leif Appelgren</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136097892</t>
+          <t>https://artportalen.se/Sighting/132335133</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>136097894</v>
+        <v>136707423</v>
       </c>
       <c r="B61" t="n">
-        <v>102471</v>
+        <v>106399</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>221235</v>
+        <v>221141</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Väst om Rannebergets naturreservat, Dls</t>
+          <t>Väster om Rannebergets NR, Dls</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>348605</v>
+        <v>348660</v>
       </c>
       <c r="R61" t="n">
-        <v>6519385</v>
+        <v>6519138</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7167,12 +7167,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7198,38 +7198,38 @@
       <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136097894</t>
+          <t>https://artportalen.se/Sighting/136707423</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>136097901</v>
+        <v>136097904</v>
       </c>
       <c r="B62" t="n">
-        <v>102471</v>
+        <v>106487</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>221235</v>
+        <v>221144</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7239,10 +7239,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>348632</v>
+        <v>348602</v>
       </c>
       <c r="R62" t="n">
-        <v>6519294</v>
+        <v>6519311</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -7300,16 +7300,16 @@
       <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136097901</t>
+          <t>https://artportalen.se/Sighting/136097904</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>136097903</v>
+        <v>136097886</v>
       </c>
       <c r="B63" t="n">
-        <v>102471</v>
+        <v>102472</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7341,10 +7341,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>348624</v>
+        <v>348812</v>
       </c>
       <c r="R63" t="n">
-        <v>6519288</v>
+        <v>6519662</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -7402,16 +7402,16 @@
       <c r="AY63" t="inlineStr"/>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136097903</t>
+          <t>https://artportalen.se/Sighting/136097886</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>136097913</v>
+        <v>136097892</v>
       </c>
       <c r="B64" t="n">
-        <v>102471</v>
+        <v>102472</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7443,10 +7443,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>348537</v>
+        <v>348607</v>
       </c>
       <c r="R64" t="n">
-        <v>6519535</v>
+        <v>6519437</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7504,16 +7504,16 @@
       <c r="AY64" t="inlineStr"/>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136097913</t>
+          <t>https://artportalen.se/Sighting/136097892</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>136097916</v>
+        <v>136097894</v>
       </c>
       <c r="B65" t="n">
-        <v>102471</v>
+        <v>102472</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7545,10 +7545,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>348527</v>
+        <v>348605</v>
       </c>
       <c r="R65" t="n">
-        <v>6519500</v>
+        <v>6519385</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -7606,16 +7606,16 @@
       <c r="AY65" t="inlineStr"/>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136097916</t>
+          <t>https://artportalen.se/Sighting/136097894</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>136098084</v>
+        <v>136097901</v>
       </c>
       <c r="B66" t="n">
-        <v>102471</v>
+        <v>102472</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7647,10 +7647,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>348668</v>
+        <v>348632</v>
       </c>
       <c r="R66" t="n">
-        <v>6519210</v>
+        <v>6519294</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -7708,38 +7708,38 @@
       <c r="AY66" t="inlineStr"/>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136098084</t>
+          <t>https://artportalen.se/Sighting/136097901</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>136097902</v>
+        <v>136097903</v>
       </c>
       <c r="B67" t="n">
-        <v>104355</v>
+        <v>102472</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>221987</v>
+        <v>221235</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Skogsbingel</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Mercurialis perennis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7810,64 +7810,54 @@
       <c r="AY67" t="inlineStr"/>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136097902</t>
+          <t>https://artportalen.se/Sighting/136097903</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>121791393</v>
+        <v>136097913</v>
       </c>
       <c r="B68" t="n">
-        <v>101326</v>
+        <v>102472</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>222498</v>
+        <v>221235</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N68" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Janses kulle, Janses kulle, Dls</t>
+          <t>Väst om Rannebergets naturreservat, Dls</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>348597</v>
+        <v>348537</v>
       </c>
       <c r="R68" t="n">
-        <v>6519354</v>
+        <v>6519535</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7891,12 +7881,12 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2024-12-30</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2024-12-30</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7907,71 +7897,66 @@
       </c>
       <c r="AG68" t="b">
         <v>0</v>
-      </c>
-      <c r="AH68" t="inlineStr">
-        <is>
-          <t>Barr-/lövbland</t>
-        </is>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121791393</t>
+          <t>https://artportalen.se/Sighting/136097913</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>132446006</v>
+        <v>136097916</v>
       </c>
       <c r="B69" t="n">
-        <v>101403</v>
+        <v>102472</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>222498</v>
+        <v>221235</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Janses kulle, Dls</t>
+          <t>Väst om Rannebergets naturreservat, Dls</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>348630</v>
+        <v>348527</v>
       </c>
       <c r="R69" t="n">
-        <v>6519376</v>
+        <v>6519500</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -7998,12 +7983,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8029,51 +8014,51 @@
       <c r="AY69" t="inlineStr"/>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132446006</t>
+          <t>https://artportalen.se/Sighting/136097916</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>132446030</v>
+        <v>136098084</v>
       </c>
       <c r="B70" t="n">
-        <v>101403</v>
+        <v>102472</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>222498</v>
+        <v>221235</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Skårdalens gamla tomt, Dls</t>
+          <t>Väst om Rannebergets naturreservat, Dls</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>348675</v>
+        <v>348668</v>
       </c>
       <c r="R70" t="n">
-        <v>6519199</v>
+        <v>6519210</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -8100,12 +8085,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8131,16 +8116,16 @@
       <c r="AY70" t="inlineStr"/>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132446030</t>
+          <t>https://artportalen.se/Sighting/136098084</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>132446073</v>
+        <v>136097902</v>
       </c>
       <c r="B71" t="n">
-        <v>101403</v>
+        <v>104356</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8148,34 +8133,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>222498</v>
+        <v>221987</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogsbingel</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Mercurialis perennis</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Skog söder om Lilla Skårsdalstjärnet, Dls</t>
+          <t>Väst om Rannebergets naturreservat, Dls</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>348729</v>
+        <v>348624</v>
       </c>
       <c r="R71" t="n">
-        <v>6519685</v>
+        <v>6519288</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -8202,12 +8187,12 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8233,16 +8218,16 @@
       <c r="AY71" t="inlineStr"/>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132446073</t>
+          <t>https://artportalen.se/Sighting/136097902</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>136097895</v>
+        <v>121791393</v>
       </c>
       <c r="B72" t="n">
-        <v>101555</v>
+        <v>101326</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8268,19 +8253,29 @@
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Väst om Rannebergets naturreservat, Dls</t>
+          <t>Janses kulle, Janses kulle, Dls</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>348593</v>
+        <v>348597</v>
       </c>
       <c r="R72" t="n">
-        <v>6519392</v>
+        <v>6519354</v>
       </c>
       <c r="S72" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8304,12 +8299,12 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2024-12-30</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2024-12-30</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8320,31 +8315,36 @@
       </c>
       <c r="AG72" t="b">
         <v>0</v>
+      </c>
+      <c r="AH72" t="inlineStr">
+        <is>
+          <t>Barr-/lövbland</t>
+        </is>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136097895</t>
+          <t>https://artportalen.se/Sighting/121791393</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>136097917</v>
+        <v>132446006</v>
       </c>
       <c r="B73" t="n">
-        <v>101555</v>
+        <v>101403</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8372,14 +8372,14 @@
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Väst om Rannebergets naturreservat, Dls</t>
+          <t>Janses kulle, Dls</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>348527</v>
+        <v>348630</v>
       </c>
       <c r="R73" t="n">
-        <v>6519500</v>
+        <v>6519376</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -8406,12 +8406,12 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8437,16 +8437,16 @@
       <c r="AY73" t="inlineStr"/>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136097917</t>
+          <t>https://artportalen.se/Sighting/132446006</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>136097919</v>
+        <v>132446030</v>
       </c>
       <c r="B74" t="n">
-        <v>101555</v>
+        <v>101403</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8474,14 +8474,14 @@
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Väst om Rannebergets naturreservat, Dls</t>
+          <t>Skårdalens gamla tomt, Dls</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>348541</v>
+        <v>348675</v>
       </c>
       <c r="R74" t="n">
-        <v>6519474</v>
+        <v>6519199</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -8508,12 +8508,12 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8539,16 +8539,16 @@
       <c r="AY74" t="inlineStr"/>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136097919</t>
+          <t>https://artportalen.se/Sighting/132446030</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>136097920</v>
+        <v>132446073</v>
       </c>
       <c r="B75" t="n">
-        <v>101555</v>
+        <v>101403</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8576,14 +8576,14 @@
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Väst om Rannebergets naturreservat, Dls</t>
+          <t>Skog söder om Lilla Skårsdalstjärnet, Dls</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>348563</v>
+        <v>348729</v>
       </c>
       <c r="R75" t="n">
-        <v>6519496</v>
+        <v>6519685</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -8610,12 +8610,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8641,16 +8641,16 @@
       <c r="AY75" t="inlineStr"/>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136097920</t>
+          <t>https://artportalen.se/Sighting/132446073</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>136097940</v>
+        <v>136097895</v>
       </c>
       <c r="B76" t="n">
-        <v>101555</v>
+        <v>101556</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8682,10 +8682,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>348759</v>
+        <v>348593</v>
       </c>
       <c r="R76" t="n">
-        <v>6519595</v>
+        <v>6519392</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -8743,16 +8743,16 @@
       <c r="AY76" t="inlineStr"/>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136097940</t>
+          <t>https://artportalen.se/Sighting/136097895</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>136097945</v>
+        <v>136097917</v>
       </c>
       <c r="B77" t="n">
-        <v>101555</v>
+        <v>101556</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8784,10 +8784,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>348840</v>
+        <v>348527</v>
       </c>
       <c r="R77" t="n">
-        <v>6519584</v>
+        <v>6519500</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -8845,16 +8845,16 @@
       <c r="AY77" t="inlineStr"/>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136097945</t>
+          <t>https://artportalen.se/Sighting/136097917</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>136097888</v>
+        <v>136097919</v>
       </c>
       <c r="B78" t="n">
-        <v>101457</v>
+        <v>101556</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8862,21 +8862,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>222771</v>
+        <v>222498</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8886,10 +8886,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>348854</v>
+        <v>348541</v>
       </c>
       <c r="R78" t="n">
-        <v>6519653</v>
+        <v>6519474</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -8947,16 +8947,16 @@
       <c r="AY78" t="inlineStr"/>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136097888</t>
+          <t>https://artportalen.se/Sighting/136097919</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>136097935</v>
+        <v>136097920</v>
       </c>
       <c r="B79" t="n">
-        <v>101457</v>
+        <v>101556</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8964,21 +8964,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>222771</v>
+        <v>222498</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8988,10 +8988,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>348713</v>
+        <v>348563</v>
       </c>
       <c r="R79" t="n">
-        <v>6519667</v>
+        <v>6519496</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -9049,16 +9049,16 @@
       <c r="AY79" t="inlineStr"/>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136097935</t>
+          <t>https://artportalen.se/Sighting/136097920</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>136097937</v>
+        <v>136097940</v>
       </c>
       <c r="B80" t="n">
-        <v>101457</v>
+        <v>101556</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9066,21 +9066,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>222771</v>
+        <v>222498</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9090,10 +9090,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>348713</v>
+        <v>348759</v>
       </c>
       <c r="R80" t="n">
-        <v>6519650</v>
+        <v>6519595</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -9151,16 +9151,16 @@
       <c r="AY80" t="inlineStr"/>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136097937</t>
+          <t>https://artportalen.se/Sighting/136097940</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>132446009</v>
+        <v>136097945</v>
       </c>
       <c r="B81" t="n">
-        <v>80438</v>
+        <v>101556</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9168,34 +9168,34 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>229497</v>
+        <v>222498</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Janses kulle, Dls</t>
+          <t>Väst om Rannebergets naturreservat, Dls</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>348626</v>
+        <v>348840</v>
       </c>
       <c r="R81" t="n">
-        <v>6519358</v>
+        <v>6519584</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -9222,12 +9222,12 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9238,21 +9238,6 @@
       </c>
       <c r="AG81" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ81" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK81" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO81" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
@@ -9268,16 +9253,16 @@
       <c r="AY81" t="inlineStr"/>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132446009</t>
+          <t>https://artportalen.se/Sighting/136097945</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>132446014</v>
+        <v>136097888</v>
       </c>
       <c r="B82" t="n">
-        <v>80403</v>
+        <v>101458</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9285,34 +9270,34 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6003719</v>
+        <v>222771</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Traslav</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Scytinium lichenoides</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) Otálora, P.M.Jørg. &amp; Wedin</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Janses kulle, Dls</t>
+          <t>Väst om Rannebergets naturreservat, Dls</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>348655</v>
+        <v>348854</v>
       </c>
       <c r="R82" t="n">
-        <v>6519352</v>
+        <v>6519653</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>
@@ -9339,12 +9324,12 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9355,21 +9340,6 @@
       </c>
       <c r="AG82" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ82" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK82" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO82" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
@@ -9384,6 +9354,444 @@
       </c>
       <c r="AY82" t="inlineStr"/>
       <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136097888</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>136097935</v>
+      </c>
+      <c r="B83" t="n">
+        <v>101458</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Väst om Rannebergets naturreservat, Dls</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>348713</v>
+      </c>
+      <c r="R83" t="n">
+        <v>6519667</v>
+      </c>
+      <c r="S83" t="n">
+        <v>5</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Mellerud</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Dalskog</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136097935</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>136097937</v>
+      </c>
+      <c r="B84" t="n">
+        <v>101458</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Väst om Rannebergets naturreservat, Dls</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>348713</v>
+      </c>
+      <c r="R84" t="n">
+        <v>6519650</v>
+      </c>
+      <c r="S84" t="n">
+        <v>5</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Mellerud</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Dalskog</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136097937</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>132446009</v>
+      </c>
+      <c r="B85" t="n">
+        <v>80438</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Janses kulle, Dls</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>348626</v>
+      </c>
+      <c r="R85" t="n">
+        <v>6519358</v>
+      </c>
+      <c r="S85" t="n">
+        <v>5</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Mellerud</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Dalskog</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ85" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK85" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO85" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132446009</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>132446014</v>
+      </c>
+      <c r="B86" t="n">
+        <v>80403</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>6003719</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Traslav</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Scytinium lichenoides</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>(L.) Otálora, P.M.Jørg. &amp; Wedin</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Janses kulle, Dls</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>348655</v>
+      </c>
+      <c r="R86" t="n">
+        <v>6519352</v>
+      </c>
+      <c r="S86" t="n">
+        <v>5</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Mellerud</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Dalskog</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ86" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK86" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO86" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/132446014</t>
         </is>
@@ -9472,6 +9880,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 26678-2026 artfynd.xlsx
+++ b/artfynd/A 26678-2026 artfynd.xlsx
@@ -2322,7 +2322,7 @@
         <v>136707418</v>
       </c>
       <c r="B17" t="n">
-        <v>96660</v>
+        <v>96665</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2934,7 +2934,7 @@
         <v>136707412</v>
       </c>
       <c r="B23" t="n">
-        <v>96649</v>
+        <v>96654</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -4572,7 +4572,7 @@
         <v>136101564</v>
       </c>
       <c r="B38" t="n">
-        <v>92163</v>
+        <v>92168</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5876,7 +5876,7 @@
         <v>136707427</v>
       </c>
       <c r="B49" t="n">
-        <v>107856</v>
+        <v>107861</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -7105,7 +7105,7 @@
         <v>136707423</v>
       </c>
       <c r="B61" t="n">
-        <v>106399</v>
+        <v>106404</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>

--- a/artfynd/A 26678-2026 artfynd.xlsx
+++ b/artfynd/A 26678-2026 artfynd.xlsx
@@ -2322,7 +2322,7 @@
         <v>136707418</v>
       </c>
       <c r="B17" t="n">
-        <v>96665</v>
+        <v>96667</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2934,7 +2934,7 @@
         <v>136707412</v>
       </c>
       <c r="B23" t="n">
-        <v>96654</v>
+        <v>96656</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -5876,7 +5876,7 @@
         <v>136707427</v>
       </c>
       <c r="B49" t="n">
-        <v>107861</v>
+        <v>107863</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -7105,7 +7105,7 @@
         <v>136707423</v>
       </c>
       <c r="B61" t="n">
-        <v>106404</v>
+        <v>106406</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>

--- a/artfynd/A 26678-2026 artfynd.xlsx
+++ b/artfynd/A 26678-2026 artfynd.xlsx
@@ -2322,7 +2322,7 @@
         <v>136707418</v>
       </c>
       <c r="B17" t="n">
-        <v>96667</v>
+        <v>96673</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2934,7 +2934,7 @@
         <v>136707412</v>
       </c>
       <c r="B23" t="n">
-        <v>96656</v>
+        <v>96662</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -5876,7 +5876,7 @@
         <v>136707427</v>
       </c>
       <c r="B49" t="n">
-        <v>107863</v>
+        <v>107869</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -7105,7 +7105,7 @@
         <v>136707423</v>
       </c>
       <c r="B61" t="n">
-        <v>106406</v>
+        <v>106412</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>

--- a/artfynd/A 26678-2026 artfynd.xlsx
+++ b/artfynd/A 26678-2026 artfynd.xlsx
@@ -2322,7 +2322,7 @@
         <v>136707418</v>
       </c>
       <c r="B17" t="n">
-        <v>96673</v>
+        <v>96675</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2934,7 +2934,7 @@
         <v>136707412</v>
       </c>
       <c r="B23" t="n">
-        <v>96662</v>
+        <v>96664</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -5876,7 +5876,7 @@
         <v>136707427</v>
       </c>
       <c r="B49" t="n">
-        <v>107869</v>
+        <v>107871</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -7105,7 +7105,7 @@
         <v>136707423</v>
       </c>
       <c r="B61" t="n">
-        <v>106412</v>
+        <v>106414</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>

--- a/artfynd/A 26678-2026 artfynd.xlsx
+++ b/artfynd/A 26678-2026 artfynd.xlsx
@@ -4690,7 +4690,7 @@
         <v>132446023</v>
       </c>
       <c r="B39" t="n">
-        <v>4776</v>
+        <v>4777</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4812,7 +4812,7 @@
         <v>132446079</v>
       </c>
       <c r="B40" t="n">
-        <v>4776</v>
+        <v>4777</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4934,7 +4934,7 @@
         <v>132446074</v>
       </c>
       <c r="B41" t="n">
-        <v>5181</v>
+        <v>5182</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 26678-2026 artfynd.xlsx
+++ b/artfynd/A 26678-2026 artfynd.xlsx
@@ -2322,7 +2322,7 @@
         <v>136707418</v>
       </c>
       <c r="B17" t="n">
-        <v>96675</v>
+        <v>96676</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2934,7 +2934,7 @@
         <v>136707412</v>
       </c>
       <c r="B23" t="n">
-        <v>96664</v>
+        <v>96665</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -5876,7 +5876,7 @@
         <v>136707427</v>
       </c>
       <c r="B49" t="n">
-        <v>107871</v>
+        <v>107872</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -7105,7 +7105,7 @@
         <v>136707423</v>
       </c>
       <c r="B61" t="n">
-        <v>106414</v>
+        <v>106415</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>

--- a/artfynd/A 26678-2026 artfynd.xlsx
+++ b/artfynd/A 26678-2026 artfynd.xlsx
@@ -2322,7 +2322,7 @@
         <v>136707418</v>
       </c>
       <c r="B17" t="n">
-        <v>96676</v>
+        <v>96682</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2934,7 +2934,7 @@
         <v>136707412</v>
       </c>
       <c r="B23" t="n">
-        <v>96665</v>
+        <v>96671</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -5876,7 +5876,7 @@
         <v>136707427</v>
       </c>
       <c r="B49" t="n">
-        <v>107872</v>
+        <v>107878</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -7105,7 +7105,7 @@
         <v>136707423</v>
       </c>
       <c r="B61" t="n">
-        <v>106415</v>
+        <v>106421</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>

--- a/artfynd/A 26678-2026 artfynd.xlsx
+++ b/artfynd/A 26678-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ86"/>
+  <dimension ref="A1:AZ98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2322,7 +2322,7 @@
         <v>136707418</v>
       </c>
       <c r="B17" t="n">
-        <v>96682</v>
+        <v>96686</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2934,7 +2934,7 @@
         <v>136707412</v>
       </c>
       <c r="B23" t="n">
-        <v>96671</v>
+        <v>96675</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -4215,10 +4215,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132446025</v>
+        <v>137153563</v>
       </c>
       <c r="B35" t="n">
-        <v>92031</v>
+        <v>93098</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4226,34 +4226,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5321</v>
+        <v>4769</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Skårdalens gamla tomt, Dls</t>
+          <t>Väst om Ranneberget, Dls</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>348701</v>
+        <v>348617</v>
       </c>
       <c r="R35" t="n">
-        <v>6519282</v>
+        <v>6519485</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4280,12 +4280,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4294,24 +4294,8 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
@@ -4327,16 +4311,16 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132446025</t>
+          <t>https://artportalen.se/Sighting/137153563</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132446026</v>
+        <v>137153564</v>
       </c>
       <c r="B36" t="n">
-        <v>92031</v>
+        <v>93098</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4344,34 +4328,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5321</v>
+        <v>4769</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Skårdalens gamla tomt, Dls</t>
+          <t>Väst om Ranneberget, Dls</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>348708</v>
+        <v>348585</v>
       </c>
       <c r="R36" t="n">
-        <v>6519267</v>
+        <v>6519443</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4398,12 +4382,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4412,24 +4396,8 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ36" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK36" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
@@ -4445,16 +4413,16 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132446026</t>
+          <t>https://artportalen.se/Sighting/137153564</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132446028</v>
+        <v>137153568</v>
       </c>
       <c r="B37" t="n">
-        <v>92031</v>
+        <v>93098</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4462,34 +4430,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5321</v>
+        <v>4769</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Skårdalens gamla tomt, Dls</t>
+          <t>Väst om Ranneberget, Dls</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>348666</v>
+        <v>348584</v>
       </c>
       <c r="R37" t="n">
-        <v>6519254</v>
+        <v>6519354</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4516,12 +4484,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4530,24 +4498,8 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ37" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK37" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO37" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
@@ -4563,16 +4515,16 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132446028</t>
+          <t>https://artportalen.se/Sighting/137153568</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>136101564</v>
+        <v>137153569</v>
       </c>
       <c r="B38" t="n">
-        <v>92168</v>
+        <v>93098</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4580,21 +4532,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5321</v>
+        <v>4769</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4604,10 +4556,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>348774</v>
+        <v>348594</v>
       </c>
       <c r="R38" t="n">
-        <v>6519585</v>
+        <v>6519310</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4634,12 +4586,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4648,24 +4600,8 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ38" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK38" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
@@ -4681,16 +4617,16 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136101564</t>
+          <t>https://artportalen.se/Sighting/137153569</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132446023</v>
+        <v>137153570</v>
       </c>
       <c r="B39" t="n">
-        <v>4777</v>
+        <v>93098</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4698,39 +4634,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100299</v>
+        <v>4769</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Skårdalens gamla tomt, Dls</t>
+          <t>Väst om Ranneberget, Dls</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>348665</v>
+        <v>348609</v>
       </c>
       <c r="R39" t="n">
-        <v>6519298</v>
+        <v>6519301</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4757,12 +4688,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4773,21 +4704,6 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ39" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK39" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO39" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
@@ -4803,16 +4719,16 @@
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132446023</t>
+          <t>https://artportalen.se/Sighting/137153570</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132446079</v>
+        <v>137153581</v>
       </c>
       <c r="B40" t="n">
-        <v>4777</v>
+        <v>93098</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4820,39 +4736,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100299</v>
+        <v>4769</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Barrskogen mellan Lilla Skårsdalstjärnet och Kvarntjärnet, Dls</t>
+          <t>Väst om Ranneberget, Dls</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>348740</v>
+        <v>348710</v>
       </c>
       <c r="R40" t="n">
-        <v>6519761</v>
+        <v>6519717</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4879,12 +4790,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4895,21 +4806,6 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ40" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK40" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
@@ -4925,16 +4821,16 @@
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132446079</t>
+          <t>https://artportalen.se/Sighting/137153581</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132446074</v>
+        <v>137153582</v>
       </c>
       <c r="B41" t="n">
-        <v>5182</v>
+        <v>93098</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4942,39 +4838,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100526</v>
+        <v>4769</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Barrskogen mellan Lilla Skårsdalstjärnet och Kvarntjärnet, Dls</t>
+          <t>Väst om Ranneberget, Dls</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>348747</v>
+        <v>348724</v>
       </c>
       <c r="R41" t="n">
-        <v>6519747</v>
+        <v>6519710</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5001,12 +4892,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5015,24 +4906,8 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
@@ -5048,16 +4923,16 @@
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132446074</t>
+          <t>https://artportalen.se/Sighting/137153582</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>136097897</v>
+        <v>137153584</v>
       </c>
       <c r="B42" t="n">
-        <v>5182</v>
+        <v>93098</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5065,39 +4940,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100526</v>
+        <v>4769</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Väst om Rannebergets naturreservat, Dls</t>
+          <t>Väst om Ranneberget, Dls</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>348723</v>
+        <v>348722</v>
       </c>
       <c r="R42" t="n">
-        <v>6519121</v>
+        <v>6519683</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5124,12 +4994,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5140,21 +5010,6 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ42" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK42" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO42" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
@@ -5170,16 +5025,16 @@
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136097897</t>
+          <t>https://artportalen.se/Sighting/137153584</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>136097898</v>
+        <v>132446025</v>
       </c>
       <c r="B43" t="n">
-        <v>5202</v>
+        <v>92031</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5187,39 +5042,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>105930</v>
+        <v>5321</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Väst om Rannebergets naturreservat, Dls</t>
+          <t>Skårdalens gamla tomt, Dls</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>348723</v>
+        <v>348701</v>
       </c>
       <c r="R43" t="n">
-        <v>6519121</v>
+        <v>6519282</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5246,12 +5096,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5260,22 +5110,23 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -5292,16 +5143,16 @@
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136097898</t>
+          <t>https://artportalen.se/Sighting/132446025</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>136097942</v>
+        <v>132446026</v>
       </c>
       <c r="B44" t="n">
-        <v>5202</v>
+        <v>92031</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5309,39 +5160,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>105930</v>
+        <v>5321</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Väst om Rannebergets naturreservat, Dls</t>
+          <t>Skårdalens gamla tomt, Dls</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>348780</v>
+        <v>348708</v>
       </c>
       <c r="R44" t="n">
-        <v>6519577</v>
+        <v>6519267</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5368,12 +5214,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5382,22 +5228,23 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK44" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -5414,56 +5261,51 @@
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136097942</t>
+          <t>https://artportalen.se/Sighting/132446026</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>132445999</v>
+        <v>132446028</v>
       </c>
       <c r="B45" t="n">
-        <v>8374</v>
+        <v>92031</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>106540</v>
+        <v>5321</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Svart askbastborre</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hylesinus crenatus</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fabricius, 1787)</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Janses kulle, Dls</t>
+          <t>Skårdalens gamla tomt, Dls</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>348665</v>
+        <v>348666</v>
       </c>
       <c r="R45" t="n">
-        <v>6519431</v>
+        <v>6519254</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5504,22 +5346,23 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>ask</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -5536,56 +5379,51 @@
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132445999</t>
+          <t>https://artportalen.se/Sighting/132446028</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>132446029</v>
+        <v>136101564</v>
       </c>
       <c r="B46" t="n">
-        <v>8374</v>
+        <v>92168</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>106540</v>
+        <v>5321</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Svart askbastborre</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hylesinus crenatus</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fabricius, 1787)</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Skårdalens gamla tomt, Dls</t>
+          <t>Väst om Ranneberget, Dls</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>348623</v>
+        <v>348774</v>
       </c>
       <c r="R46" t="n">
-        <v>6519241</v>
+        <v>6519585</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5612,12 +5450,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5626,22 +5464,23 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>ask</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -5658,16 +5497,16 @@
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132446029</t>
+          <t>https://artportalen.se/Sighting/136101564</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>132446075</v>
+        <v>137153585</v>
       </c>
       <c r="B47" t="n">
-        <v>8449</v>
+        <v>93157</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5675,34 +5514,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>106554</v>
+        <v>5836</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Guldkremla</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Russula aurea</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Pers.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Barrskogen mellan Lilla Skårsdalstjärnet och Kvarntjärnet, Dls</t>
+          <t>Väst om Ranneberget, Dls</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>348741</v>
+        <v>348798</v>
       </c>
       <c r="R47" t="n">
-        <v>6519743</v>
+        <v>6519665</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5729,12 +5568,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5760,16 +5599,16 @@
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132446075</t>
+          <t>https://artportalen.se/Sighting/137153585</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>136097896</v>
+        <v>132446023</v>
       </c>
       <c r="B48" t="n">
-        <v>8452</v>
+        <v>4777</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5777,21 +5616,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>106554</v>
+        <v>100299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5802,14 +5641,14 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Väst om Rannebergets naturreservat, Dls</t>
+          <t>Skårdalens gamla tomt, Dls</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>348699</v>
+        <v>348665</v>
       </c>
       <c r="R48" t="n">
-        <v>6519187</v>
+        <v>6519298</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5836,12 +5675,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5852,6 +5691,21 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
@@ -5867,16 +5721,16 @@
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136097896</t>
+          <t>https://artportalen.se/Sighting/132446023</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>136707427</v>
+        <v>132446079</v>
       </c>
       <c r="B49" t="n">
-        <v>107878</v>
+        <v>4777</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5884,34 +5738,39 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>219686</v>
+        <v>100299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vätteros</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lathraea squamaria</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Väster om Rannebergets NR, Dls</t>
+          <t>Barrskogen mellan Lilla Skårsdalstjärnet och Kvarntjärnet, Dls</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>348620</v>
+        <v>348740</v>
       </c>
       <c r="R49" t="n">
-        <v>6519302</v>
+        <v>6519761</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5938,12 +5797,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5954,6 +5813,21 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
@@ -5969,51 +5843,56 @@
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136707427</t>
+          <t>https://artportalen.se/Sighting/132446079</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>136097889</v>
+        <v>132446074</v>
       </c>
       <c r="B50" t="n">
-        <v>111644</v>
+        <v>5182</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>219711</v>
+        <v>100526</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Väst om Rannebergets naturreservat, Dls</t>
+          <t>Barrskogen mellan Lilla Skårsdalstjärnet och Kvarntjärnet, Dls</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>348824</v>
+        <v>348747</v>
       </c>
       <c r="R50" t="n">
-        <v>6519586</v>
+        <v>6519747</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6040,12 +5919,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6054,8 +5933,24 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
@@ -6071,51 +5966,56 @@
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136097889</t>
+          <t>https://artportalen.se/Sighting/132446074</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>136097891</v>
+        <v>136097897</v>
       </c>
       <c r="B51" t="n">
-        <v>111644</v>
+        <v>5182</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>219711</v>
+        <v>100526</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Väst om Rannebergets naturreservat, Dls</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>348614</v>
+        <v>348723</v>
       </c>
       <c r="R51" t="n">
-        <v>6519482</v>
+        <v>6519121</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6159,6 +6059,21 @@
       <c r="AG51" t="b">
         <v>0</v>
       </c>
+      <c r="AJ51" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK51" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO51" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
@@ -6173,51 +6088,56 @@
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136097891</t>
+          <t>https://artportalen.se/Sighting/136097897</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>136097893</v>
+        <v>136097898</v>
       </c>
       <c r="B52" t="n">
-        <v>111644</v>
+        <v>5202</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>219711</v>
+        <v>105930</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Väst om Rannebergets naturreservat, Dls</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>348612</v>
+        <v>348723</v>
       </c>
       <c r="R52" t="n">
-        <v>6519392</v>
+        <v>6519121</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6261,6 +6181,21 @@
       <c r="AG52" t="b">
         <v>0</v>
       </c>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK52" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
@@ -6275,51 +6210,56 @@
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136097893</t>
+          <t>https://artportalen.se/Sighting/136097898</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>136097900</v>
+        <v>136097942</v>
       </c>
       <c r="B53" t="n">
-        <v>111644</v>
+        <v>5202</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>219711</v>
+        <v>105930</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Väst om Rannebergets naturreservat, Dls</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>348618</v>
+        <v>348780</v>
       </c>
       <c r="R53" t="n">
-        <v>6519260</v>
+        <v>6519577</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6363,6 +6303,21 @@
       <c r="AG53" t="b">
         <v>0</v>
       </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
@@ -6377,16 +6332,16 @@
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136097900</t>
+          <t>https://artportalen.se/Sighting/136097942</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>136097921</v>
+        <v>132445999</v>
       </c>
       <c r="B54" t="n">
-        <v>111644</v>
+        <v>8374</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6394,34 +6349,39 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>219711</v>
+        <v>106540</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Svart askbastborre</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hylesinus crenatus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fabricius, 1787)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Väst om Rannebergets naturreservat, Dls</t>
+          <t>Janses kulle, Dls</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>348587</v>
+        <v>348665</v>
       </c>
       <c r="R54" t="n">
-        <v>6519511</v>
+        <v>6519431</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6448,12 +6408,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6464,6 +6424,21 @@
       </c>
       <c r="AG54" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ54" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK54" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO54" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
@@ -6479,16 +6454,16 @@
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136097921</t>
+          <t>https://artportalen.se/Sighting/132445999</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>136097933</v>
+        <v>132446029</v>
       </c>
       <c r="B55" t="n">
-        <v>111644</v>
+        <v>8374</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6496,34 +6471,39 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>219711</v>
+        <v>106540</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Svart askbastborre</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hylesinus crenatus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fabricius, 1787)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Väst om Rannebergets naturreservat, Dls</t>
+          <t>Skårdalens gamla tomt, Dls</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>348673</v>
+        <v>348623</v>
       </c>
       <c r="R55" t="n">
-        <v>6519697</v>
+        <v>6519241</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6550,12 +6530,12 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6566,6 +6546,21 @@
       </c>
       <c r="AG55" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ55" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK55" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO55" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
@@ -6581,51 +6576,51 @@
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136097933</t>
+          <t>https://artportalen.se/Sighting/132446029</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>136097936</v>
+        <v>132446075</v>
       </c>
       <c r="B56" t="n">
-        <v>111644</v>
+        <v>8449</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>219711</v>
+        <v>106554</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Väst om Rannebergets naturreservat, Dls</t>
+          <t>Barrskogen mellan Lilla Skårsdalstjärnet och Kvarntjärnet, Dls</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>348711</v>
+        <v>348741</v>
       </c>
       <c r="R56" t="n">
-        <v>6519665</v>
+        <v>6519743</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6652,12 +6647,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6683,51 +6678,56 @@
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136097936</t>
+          <t>https://artportalen.se/Sighting/132446075</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>136097939</v>
+        <v>136097896</v>
       </c>
       <c r="B57" t="n">
-        <v>111644</v>
+        <v>8452</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>219711</v>
+        <v>106554</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Väst om Rannebergets naturreservat, Dls</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>348745</v>
+        <v>348699</v>
       </c>
       <c r="R57" t="n">
-        <v>6519603</v>
+        <v>6519187</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6785,33 +6785,33 @@
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136097939</t>
+          <t>https://artportalen.se/Sighting/136097896</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>136097943</v>
+        <v>136707427</v>
       </c>
       <c r="B58" t="n">
-        <v>111644</v>
+        <v>107882</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>219711</v>
+        <v>219686</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Vätteros</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Lathraea squamaria</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -6822,14 +6822,14 @@
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Väst om Rannebergets naturreservat, Dls</t>
+          <t>Väster om Rannebergets NR, Dls</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>348818</v>
+        <v>348620</v>
       </c>
       <c r="R58" t="n">
-        <v>6519588</v>
+        <v>6519302</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6856,12 +6856,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6887,13 +6887,13 @@
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136097943</t>
+          <t>https://artportalen.se/Sighting/136707427</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>136097946</v>
+        <v>136097889</v>
       </c>
       <c r="B59" t="n">
         <v>111644</v>
@@ -6928,10 +6928,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>348846</v>
+        <v>348824</v>
       </c>
       <c r="R59" t="n">
-        <v>6519619</v>
+        <v>6519586</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -6989,16 +6989,16 @@
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136097946</t>
+          <t>https://artportalen.se/Sighting/136097889</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>132335133</v>
+        <v>136097891</v>
       </c>
       <c r="B60" t="n">
-        <v>101974</v>
+        <v>111644</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7006,16 +7006,16 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220075</v>
+        <v>219711</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Gullpudra</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Chrysosplenium alternifolium</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -7026,17 +7026,17 @@
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Vandringstjärnet, ca 160 m NO om tjärnets norra ände, Dls</t>
+          <t>Väst om Rannebergets naturreservat, Dls</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>348563</v>
+        <v>348614</v>
       </c>
       <c r="R60" t="n">
-        <v>6519443</v>
+        <v>6519482</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7060,12 +7060,12 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7076,53 +7076,48 @@
       </c>
       <c r="AG60" t="b">
         <v>0</v>
-      </c>
-      <c r="AI60" t="inlineStr">
-        <is>
-          <t>Sumpskog med klibbal.</t>
-        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Leif Appelgren</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Leif Appelgren</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132335133</t>
+          <t>https://artportalen.se/Sighting/136097891</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>136707423</v>
+        <v>136097893</v>
       </c>
       <c r="B61" t="n">
-        <v>106421</v>
+        <v>111644</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>221141</v>
+        <v>219711</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -7133,14 +7128,14 @@
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Väster om Rannebergets NR, Dls</t>
+          <t>Väst om Rannebergets naturreservat, Dls</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>348660</v>
+        <v>348612</v>
       </c>
       <c r="R61" t="n">
-        <v>6519138</v>
+        <v>6519392</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7167,12 +7162,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7198,38 +7193,38 @@
       <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136707423</t>
+          <t>https://artportalen.se/Sighting/136097893</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>136097904</v>
+        <v>136097900</v>
       </c>
       <c r="B62" t="n">
-        <v>106487</v>
+        <v>111644</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>221144</v>
+        <v>219711</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7239,10 +7234,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>348602</v>
+        <v>348618</v>
       </c>
       <c r="R62" t="n">
-        <v>6519311</v>
+        <v>6519260</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -7300,16 +7295,16 @@
       <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136097904</t>
+          <t>https://artportalen.se/Sighting/136097900</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>136097886</v>
+        <v>136097921</v>
       </c>
       <c r="B63" t="n">
-        <v>102472</v>
+        <v>111644</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7317,21 +7312,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>221235</v>
+        <v>219711</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7341,10 +7336,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>348812</v>
+        <v>348587</v>
       </c>
       <c r="R63" t="n">
-        <v>6519662</v>
+        <v>6519511</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -7402,16 +7397,16 @@
       <c r="AY63" t="inlineStr"/>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136097886</t>
+          <t>https://artportalen.se/Sighting/136097921</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>136097892</v>
+        <v>136097933</v>
       </c>
       <c r="B64" t="n">
-        <v>102472</v>
+        <v>111644</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7419,21 +7414,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>221235</v>
+        <v>219711</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7443,10 +7438,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>348607</v>
+        <v>348673</v>
       </c>
       <c r="R64" t="n">
-        <v>6519437</v>
+        <v>6519697</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7504,16 +7499,16 @@
       <c r="AY64" t="inlineStr"/>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136097892</t>
+          <t>https://artportalen.se/Sighting/136097933</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>136097894</v>
+        <v>136097936</v>
       </c>
       <c r="B65" t="n">
-        <v>102472</v>
+        <v>111644</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7521,21 +7516,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>221235</v>
+        <v>219711</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7545,10 +7540,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>348605</v>
+        <v>348711</v>
       </c>
       <c r="R65" t="n">
-        <v>6519385</v>
+        <v>6519665</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -7606,16 +7601,16 @@
       <c r="AY65" t="inlineStr"/>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136097894</t>
+          <t>https://artportalen.se/Sighting/136097936</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>136097901</v>
+        <v>136097939</v>
       </c>
       <c r="B66" t="n">
-        <v>102472</v>
+        <v>111644</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7623,21 +7618,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>221235</v>
+        <v>219711</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7647,10 +7642,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>348632</v>
+        <v>348745</v>
       </c>
       <c r="R66" t="n">
-        <v>6519294</v>
+        <v>6519603</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -7708,16 +7703,16 @@
       <c r="AY66" t="inlineStr"/>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136097901</t>
+          <t>https://artportalen.se/Sighting/136097939</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>136097903</v>
+        <v>136097943</v>
       </c>
       <c r="B67" t="n">
-        <v>102472</v>
+        <v>111644</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7725,21 +7720,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>221235</v>
+        <v>219711</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7749,10 +7744,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>348624</v>
+        <v>348818</v>
       </c>
       <c r="R67" t="n">
-        <v>6519288</v>
+        <v>6519588</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -7810,16 +7805,16 @@
       <c r="AY67" t="inlineStr"/>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136097903</t>
+          <t>https://artportalen.se/Sighting/136097943</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>136097913</v>
+        <v>136097946</v>
       </c>
       <c r="B68" t="n">
-        <v>102472</v>
+        <v>111644</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7827,21 +7822,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>221235</v>
+        <v>219711</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7851,10 +7846,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>348537</v>
+        <v>348846</v>
       </c>
       <c r="R68" t="n">
-        <v>6519535</v>
+        <v>6519619</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -7912,16 +7907,16 @@
       <c r="AY68" t="inlineStr"/>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136097913</t>
+          <t>https://artportalen.se/Sighting/136097946</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>136097916</v>
+        <v>137153566</v>
       </c>
       <c r="B69" t="n">
-        <v>102472</v>
+        <v>111670</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7929,34 +7924,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>221235</v>
+        <v>219711</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Väst om Rannebergets naturreservat, Dls</t>
+          <t>Väst om Ranneberget, Dls</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>348527</v>
+        <v>348590</v>
       </c>
       <c r="R69" t="n">
-        <v>6519500</v>
+        <v>6519442</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -7983,12 +7978,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8014,16 +8009,16 @@
       <c r="AY69" t="inlineStr"/>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136097916</t>
+          <t>https://artportalen.se/Sighting/137153566</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>136098084</v>
+        <v>137153583</v>
       </c>
       <c r="B70" t="n">
-        <v>102472</v>
+        <v>111670</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8031,34 +8026,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>221235</v>
+        <v>219711</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Väst om Rannebergets naturreservat, Dls</t>
+          <t>Väst om Ranneberget, Dls</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>348668</v>
+        <v>348722</v>
       </c>
       <c r="R70" t="n">
-        <v>6519210</v>
+        <v>6519700</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -8085,12 +8080,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8116,33 +8111,33 @@
       <c r="AY70" t="inlineStr"/>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136098084</t>
+          <t>https://artportalen.se/Sighting/137153583</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>136097902</v>
+        <v>132335133</v>
       </c>
       <c r="B71" t="n">
-        <v>104356</v>
+        <v>101974</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>221987</v>
+        <v>220075</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Skogsbingel</t>
+          <t>Gullpudra</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Mercurialis perennis</t>
+          <t>Chrysosplenium alternifolium</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -8153,17 +8148,17 @@
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Väst om Rannebergets naturreservat, Dls</t>
+          <t>Vandringstjärnet, ca 160 m NO om tjärnets norra ände, Dls</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>348624</v>
+        <v>348563</v>
       </c>
       <c r="R71" t="n">
-        <v>6519288</v>
+        <v>6519443</v>
       </c>
       <c r="S71" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8187,12 +8182,12 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8203,31 +8198,36 @@
       </c>
       <c r="AG71" t="b">
         <v>0</v>
+      </c>
+      <c r="AI71" t="inlineStr">
+        <is>
+          <t>Sumpskog med klibbal.</t>
+        </is>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Leif Appelgren</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Leif Appelgren</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136097902</t>
+          <t>https://artportalen.se/Sighting/132335133</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>121791393</v>
+        <v>136707423</v>
       </c>
       <c r="B72" t="n">
-        <v>101326</v>
+        <v>106425</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8235,47 +8235,37 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>222498</v>
+        <v>221141</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N72" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Janses kulle, Janses kulle, Dls</t>
+          <t>Väster om Rannebergets NR, Dls</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>348597</v>
+        <v>348660</v>
       </c>
       <c r="R72" t="n">
-        <v>6519354</v>
+        <v>6519138</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8299,12 +8289,12 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2024-12-30</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2024-12-30</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8315,36 +8305,31 @@
       </c>
       <c r="AG72" t="b">
         <v>0</v>
-      </c>
-      <c r="AH72" t="inlineStr">
-        <is>
-          <t>Barr-/lövbland</t>
-        </is>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121791393</t>
+          <t>https://artportalen.se/Sighting/136707423</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>132446006</v>
+        <v>136097904</v>
       </c>
       <c r="B73" t="n">
-        <v>101403</v>
+        <v>106487</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8352,34 +8337,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>222498</v>
+        <v>221144</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Janses kulle, Dls</t>
+          <t>Väst om Rannebergets naturreservat, Dls</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>348630</v>
+        <v>348602</v>
       </c>
       <c r="R73" t="n">
-        <v>6519376</v>
+        <v>6519311</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -8406,12 +8391,12 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8437,51 +8422,51 @@
       <c r="AY73" t="inlineStr"/>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132446006</t>
+          <t>https://artportalen.se/Sighting/136097904</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>132446030</v>
+        <v>136097886</v>
       </c>
       <c r="B74" t="n">
-        <v>101403</v>
+        <v>102472</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>222498</v>
+        <v>221235</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Skårdalens gamla tomt, Dls</t>
+          <t>Väst om Rannebergets naturreservat, Dls</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>348675</v>
+        <v>348812</v>
       </c>
       <c r="R74" t="n">
-        <v>6519199</v>
+        <v>6519662</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -8508,12 +8493,12 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8539,51 +8524,51 @@
       <c r="AY74" t="inlineStr"/>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132446030</t>
+          <t>https://artportalen.se/Sighting/136097886</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>132446073</v>
+        <v>136097892</v>
       </c>
       <c r="B75" t="n">
-        <v>101403</v>
+        <v>102472</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>222498</v>
+        <v>221235</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Skog söder om Lilla Skårsdalstjärnet, Dls</t>
+          <t>Väst om Rannebergets naturreservat, Dls</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>348729</v>
+        <v>348607</v>
       </c>
       <c r="R75" t="n">
-        <v>6519685</v>
+        <v>6519437</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -8610,12 +8595,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8641,38 +8626,38 @@
       <c r="AY75" t="inlineStr"/>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132446073</t>
+          <t>https://artportalen.se/Sighting/136097892</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>136097895</v>
+        <v>136097894</v>
       </c>
       <c r="B76" t="n">
-        <v>101556</v>
+        <v>102472</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>222498</v>
+        <v>221235</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8682,10 +8667,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>348593</v>
+        <v>348605</v>
       </c>
       <c r="R76" t="n">
-        <v>6519392</v>
+        <v>6519385</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -8743,38 +8728,38 @@
       <c r="AY76" t="inlineStr"/>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136097895</t>
+          <t>https://artportalen.se/Sighting/136097894</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>136097917</v>
+        <v>136097901</v>
       </c>
       <c r="B77" t="n">
-        <v>101556</v>
+        <v>102472</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>222498</v>
+        <v>221235</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8784,10 +8769,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>348527</v>
+        <v>348632</v>
       </c>
       <c r="R77" t="n">
-        <v>6519500</v>
+        <v>6519294</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -8845,38 +8830,38 @@
       <c r="AY77" t="inlineStr"/>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136097917</t>
+          <t>https://artportalen.se/Sighting/136097901</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>136097919</v>
+        <v>136097903</v>
       </c>
       <c r="B78" t="n">
-        <v>101556</v>
+        <v>102472</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>222498</v>
+        <v>221235</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8886,10 +8871,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>348541</v>
+        <v>348624</v>
       </c>
       <c r="R78" t="n">
-        <v>6519474</v>
+        <v>6519288</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -8947,38 +8932,38 @@
       <c r="AY78" t="inlineStr"/>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136097919</t>
+          <t>https://artportalen.se/Sighting/136097903</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>136097920</v>
+        <v>136097913</v>
       </c>
       <c r="B79" t="n">
-        <v>101556</v>
+        <v>102472</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>222498</v>
+        <v>221235</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8988,10 +8973,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>348563</v>
+        <v>348537</v>
       </c>
       <c r="R79" t="n">
-        <v>6519496</v>
+        <v>6519535</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -9049,38 +9034,38 @@
       <c r="AY79" t="inlineStr"/>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136097920</t>
+          <t>https://artportalen.se/Sighting/136097913</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>136097940</v>
+        <v>136097916</v>
       </c>
       <c r="B80" t="n">
-        <v>101556</v>
+        <v>102472</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>222498</v>
+        <v>221235</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9090,10 +9075,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>348759</v>
+        <v>348527</v>
       </c>
       <c r="R80" t="n">
-        <v>6519595</v>
+        <v>6519500</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -9151,38 +9136,38 @@
       <c r="AY80" t="inlineStr"/>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136097940</t>
+          <t>https://artportalen.se/Sighting/136097916</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>136097945</v>
+        <v>136098084</v>
       </c>
       <c r="B81" t="n">
-        <v>101556</v>
+        <v>102472</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>222498</v>
+        <v>221235</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9192,10 +9177,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>348840</v>
+        <v>348668</v>
       </c>
       <c r="R81" t="n">
-        <v>6519584</v>
+        <v>6519210</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -9253,16 +9238,16 @@
       <c r="AY81" t="inlineStr"/>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136097945</t>
+          <t>https://artportalen.se/Sighting/136098084</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>136097888</v>
+        <v>136097902</v>
       </c>
       <c r="B82" t="n">
-        <v>101458</v>
+        <v>104356</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9270,16 +9255,16 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>222771</v>
+        <v>221987</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Skogsbingel</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Mercurialis perennis</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -9294,10 +9279,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>348854</v>
+        <v>348624</v>
       </c>
       <c r="R82" t="n">
-        <v>6519653</v>
+        <v>6519288</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>
@@ -9355,16 +9340,16 @@
       <c r="AY82" t="inlineStr"/>
       <c r="AZ82" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136097888</t>
+          <t>https://artportalen.se/Sighting/136097902</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>136097935</v>
+        <v>121791393</v>
       </c>
       <c r="B83" t="n">
-        <v>101458</v>
+        <v>101326</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9372,37 +9357,47 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>222771</v>
+        <v>222498</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Väst om Rannebergets naturreservat, Dls</t>
+          <t>Janses kulle, Janses kulle, Dls</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>348713</v>
+        <v>348597</v>
       </c>
       <c r="R83" t="n">
-        <v>6519667</v>
+        <v>6519354</v>
       </c>
       <c r="S83" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9426,12 +9421,12 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2024-12-30</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2024-12-30</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9442,31 +9437,36 @@
       </c>
       <c r="AG83" t="b">
         <v>0</v>
+      </c>
+      <c r="AH83" t="inlineStr">
+        <is>
+          <t>Barr-/lövbland</t>
+        </is>
       </c>
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
       <c r="AZ83" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136097935</t>
+          <t>https://artportalen.se/Sighting/121791393</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>136097937</v>
+        <v>132446006</v>
       </c>
       <c r="B84" t="n">
-        <v>101458</v>
+        <v>101403</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9474,34 +9474,34 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>222771</v>
+        <v>222498</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Väst om Rannebergets naturreservat, Dls</t>
+          <t>Janses kulle, Dls</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>348713</v>
+        <v>348630</v>
       </c>
       <c r="R84" t="n">
-        <v>6519650</v>
+        <v>6519376</v>
       </c>
       <c r="S84" t="n">
         <v>5</v>
@@ -9528,12 +9528,12 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9559,16 +9559,16 @@
       <c r="AY84" t="inlineStr"/>
       <c r="AZ84" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136097937</t>
+          <t>https://artportalen.se/Sighting/132446006</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>132446009</v>
+        <v>132446030</v>
       </c>
       <c r="B85" t="n">
-        <v>80438</v>
+        <v>101403</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9576,34 +9576,34 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>229497</v>
+        <v>222498</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Janses kulle, Dls</t>
+          <t>Skårdalens gamla tomt, Dls</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>348626</v>
+        <v>348675</v>
       </c>
       <c r="R85" t="n">
-        <v>6519358</v>
+        <v>6519199</v>
       </c>
       <c r="S85" t="n">
         <v>5</v>
@@ -9647,21 +9647,6 @@
       <c r="AG85" t="b">
         <v>0</v>
       </c>
-      <c r="AJ85" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK85" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO85" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
@@ -9676,16 +9661,16 @@
       <c r="AY85" t="inlineStr"/>
       <c r="AZ85" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132446009</t>
+          <t>https://artportalen.se/Sighting/132446030</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>132446014</v>
+        <v>132446073</v>
       </c>
       <c r="B86" t="n">
-        <v>80403</v>
+        <v>101403</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9693,34 +9678,34 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6003719</v>
+        <v>222498</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Traslav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Scytinium lichenoides</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) Otálora, P.M.Jørg. &amp; Wedin</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Janses kulle, Dls</t>
+          <t>Skog söder om Lilla Skårsdalstjärnet, Dls</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>348655</v>
+        <v>348729</v>
       </c>
       <c r="R86" t="n">
-        <v>6519352</v>
+        <v>6519685</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>
@@ -9764,21 +9749,6 @@
       <c r="AG86" t="b">
         <v>0</v>
       </c>
-      <c r="AJ86" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK86" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO86" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
@@ -9792,6 +9762,1260 @@
       </c>
       <c r="AY86" t="inlineStr"/>
       <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132446073</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>136097895</v>
+      </c>
+      <c r="B87" t="n">
+        <v>101556</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Väst om Rannebergets naturreservat, Dls</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>348593</v>
+      </c>
+      <c r="R87" t="n">
+        <v>6519392</v>
+      </c>
+      <c r="S87" t="n">
+        <v>5</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Mellerud</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Dalskog</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136097895</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>136097917</v>
+      </c>
+      <c r="B88" t="n">
+        <v>101556</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Väst om Rannebergets naturreservat, Dls</t>
+        </is>
+      </c>
+      <c r="Q88" t="n">
+        <v>348527</v>
+      </c>
+      <c r="R88" t="n">
+        <v>6519500</v>
+      </c>
+      <c r="S88" t="n">
+        <v>5</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Mellerud</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Dalskog</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT88" t="inlineStr"/>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136097917</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>136097919</v>
+      </c>
+      <c r="B89" t="n">
+        <v>101556</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Väst om Rannebergets naturreservat, Dls</t>
+        </is>
+      </c>
+      <c r="Q89" t="n">
+        <v>348541</v>
+      </c>
+      <c r="R89" t="n">
+        <v>6519474</v>
+      </c>
+      <c r="S89" t="n">
+        <v>5</v>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Mellerud</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Dalskog</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT89" t="inlineStr"/>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136097919</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>136097920</v>
+      </c>
+      <c r="B90" t="n">
+        <v>101556</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Väst om Rannebergets naturreservat, Dls</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>348563</v>
+      </c>
+      <c r="R90" t="n">
+        <v>6519496</v>
+      </c>
+      <c r="S90" t="n">
+        <v>5</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Mellerud</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Dalskog</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT90" t="inlineStr"/>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136097920</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>136097940</v>
+      </c>
+      <c r="B91" t="n">
+        <v>101556</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Väst om Rannebergets naturreservat, Dls</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>348759</v>
+      </c>
+      <c r="R91" t="n">
+        <v>6519595</v>
+      </c>
+      <c r="S91" t="n">
+        <v>5</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Mellerud</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Dalskog</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT91" t="inlineStr"/>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136097940</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>136097945</v>
+      </c>
+      <c r="B92" t="n">
+        <v>101556</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>Väst om Rannebergets naturreservat, Dls</t>
+        </is>
+      </c>
+      <c r="Q92" t="n">
+        <v>348840</v>
+      </c>
+      <c r="R92" t="n">
+        <v>6519584</v>
+      </c>
+      <c r="S92" t="n">
+        <v>5</v>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>Mellerud</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>Dalskog</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT92" t="inlineStr"/>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136097945</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>136097888</v>
+      </c>
+      <c r="B93" t="n">
+        <v>101458</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>Väst om Rannebergets naturreservat, Dls</t>
+        </is>
+      </c>
+      <c r="Q93" t="n">
+        <v>348854</v>
+      </c>
+      <c r="R93" t="n">
+        <v>6519653</v>
+      </c>
+      <c r="S93" t="n">
+        <v>5</v>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>Mellerud</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>Dalskog</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT93" t="inlineStr"/>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX93" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136097888</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>136097935</v>
+      </c>
+      <c r="B94" t="n">
+        <v>101458</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>Väst om Rannebergets naturreservat, Dls</t>
+        </is>
+      </c>
+      <c r="Q94" t="n">
+        <v>348713</v>
+      </c>
+      <c r="R94" t="n">
+        <v>6519667</v>
+      </c>
+      <c r="S94" t="n">
+        <v>5</v>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>Mellerud</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>Dalskog</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT94" t="inlineStr"/>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX94" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136097935</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>136097937</v>
+      </c>
+      <c r="B95" t="n">
+        <v>101458</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>Väst om Rannebergets naturreservat, Dls</t>
+        </is>
+      </c>
+      <c r="Q95" t="n">
+        <v>348713</v>
+      </c>
+      <c r="R95" t="n">
+        <v>6519650</v>
+      </c>
+      <c r="S95" t="n">
+        <v>5</v>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>Mellerud</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>Dalskog</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT95" t="inlineStr"/>
+      <c r="AW95" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX95" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136097937</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>137153562</v>
+      </c>
+      <c r="B96" t="n">
+        <v>101484</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>Väst om Ranneberget, Dls</t>
+        </is>
+      </c>
+      <c r="Q96" t="n">
+        <v>348829</v>
+      </c>
+      <c r="R96" t="n">
+        <v>6519602</v>
+      </c>
+      <c r="S96" t="n">
+        <v>5</v>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>Mellerud</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>Dalskog</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AD96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT96" t="inlineStr"/>
+      <c r="AW96" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX96" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137153562</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>132446009</v>
+      </c>
+      <c r="B97" t="n">
+        <v>80438</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>Janses kulle, Dls</t>
+        </is>
+      </c>
+      <c r="Q97" t="n">
+        <v>348626</v>
+      </c>
+      <c r="R97" t="n">
+        <v>6519358</v>
+      </c>
+      <c r="S97" t="n">
+        <v>5</v>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>Mellerud</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>Dalskog</t>
+        </is>
+      </c>
+      <c r="Y97" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="AD97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ97" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK97" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO97" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AT97" t="inlineStr"/>
+      <c r="AW97" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX97" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132446009</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>132446014</v>
+      </c>
+      <c r="B98" t="n">
+        <v>80403</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>6003719</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Traslav</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Scytinium lichenoides</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>(L.) Otálora, P.M.Jørg. &amp; Wedin</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>Janses kulle, Dls</t>
+        </is>
+      </c>
+      <c r="Q98" t="n">
+        <v>348655</v>
+      </c>
+      <c r="R98" t="n">
+        <v>6519352</v>
+      </c>
+      <c r="S98" t="n">
+        <v>5</v>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>Mellerud</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W98" t="inlineStr">
+        <is>
+          <t>Dalskog</t>
+        </is>
+      </c>
+      <c r="Y98" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="AD98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ98" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK98" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO98" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AT98" t="inlineStr"/>
+      <c r="AW98" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX98" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/132446014</t>
         </is>
@@ -9884,6 +11108,18 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 26678-2026 artfynd.xlsx
+++ b/artfynd/A 26678-2026 artfynd.xlsx
@@ -2322,7 +2322,7 @@
         <v>136707418</v>
       </c>
       <c r="B17" t="n">
-        <v>96686</v>
+        <v>96688</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2934,7 +2934,7 @@
         <v>136707412</v>
       </c>
       <c r="B23" t="n">
-        <v>96675</v>
+        <v>96677</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -6794,7 +6794,7 @@
         <v>136707427</v>
       </c>
       <c r="B58" t="n">
-        <v>107882</v>
+        <v>107884</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7916,7 +7916,7 @@
         <v>137153566</v>
       </c>
       <c r="B69" t="n">
-        <v>111670</v>
+        <v>111672</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8018,7 +8018,7 @@
         <v>137153583</v>
       </c>
       <c r="B70" t="n">
-        <v>111670</v>
+        <v>111672</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8227,7 +8227,7 @@
         <v>136707423</v>
       </c>
       <c r="B72" t="n">
-        <v>106425</v>
+        <v>106427</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -10690,7 +10690,7 @@
         <v>137153562</v>
       </c>
       <c r="B96" t="n">
-        <v>101484</v>
+        <v>101486</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>

--- a/artfynd/A 26678-2026 artfynd.xlsx
+++ b/artfynd/A 26678-2026 artfynd.xlsx
@@ -2322,7 +2322,7 @@
         <v>136707418</v>
       </c>
       <c r="B17" t="n">
-        <v>96688</v>
+        <v>96690</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2934,7 +2934,7 @@
         <v>136707412</v>
       </c>
       <c r="B23" t="n">
-        <v>96677</v>
+        <v>96679</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -4218,7 +4218,7 @@
         <v>137153563</v>
       </c>
       <c r="B35" t="n">
-        <v>93098</v>
+        <v>93100</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4320,7 +4320,7 @@
         <v>137153564</v>
       </c>
       <c r="B36" t="n">
-        <v>93098</v>
+        <v>93100</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4422,7 +4422,7 @@
         <v>137153568</v>
       </c>
       <c r="B37" t="n">
-        <v>93098</v>
+        <v>93100</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4524,7 +4524,7 @@
         <v>137153569</v>
       </c>
       <c r="B38" t="n">
-        <v>93098</v>
+        <v>93100</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4626,7 +4626,7 @@
         <v>137153570</v>
       </c>
       <c r="B39" t="n">
-        <v>93098</v>
+        <v>93100</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4728,7 +4728,7 @@
         <v>137153581</v>
       </c>
       <c r="B40" t="n">
-        <v>93098</v>
+        <v>93100</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4830,7 +4830,7 @@
         <v>137153582</v>
       </c>
       <c r="B41" t="n">
-        <v>93098</v>
+        <v>93100</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4932,7 +4932,7 @@
         <v>137153584</v>
       </c>
       <c r="B42" t="n">
-        <v>93098</v>
+        <v>93100</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5506,7 +5506,7 @@
         <v>137153585</v>
       </c>
       <c r="B47" t="n">
-        <v>93157</v>
+        <v>93159</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6794,7 +6794,7 @@
         <v>136707427</v>
       </c>
       <c r="B58" t="n">
-        <v>107884</v>
+        <v>107886</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7916,7 +7916,7 @@
         <v>137153566</v>
       </c>
       <c r="B69" t="n">
-        <v>111672</v>
+        <v>111674</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8018,7 +8018,7 @@
         <v>137153583</v>
       </c>
       <c r="B70" t="n">
-        <v>111672</v>
+        <v>111674</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8227,7 +8227,7 @@
         <v>136707423</v>
       </c>
       <c r="B72" t="n">
-        <v>106427</v>
+        <v>106429</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -10690,7 +10690,7 @@
         <v>137153562</v>
       </c>
       <c r="B96" t="n">
-        <v>101486</v>
+        <v>101488</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>

--- a/artfynd/A 26678-2026 artfynd.xlsx
+++ b/artfynd/A 26678-2026 artfynd.xlsx
@@ -2322,7 +2322,7 @@
         <v>136707418</v>
       </c>
       <c r="B17" t="n">
-        <v>96690</v>
+        <v>96703</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2934,7 +2934,7 @@
         <v>136707412</v>
       </c>
       <c r="B23" t="n">
-        <v>96679</v>
+        <v>96692</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -4218,7 +4218,7 @@
         <v>137153563</v>
       </c>
       <c r="B35" t="n">
-        <v>93100</v>
+        <v>93113</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4320,7 +4320,7 @@
         <v>137153564</v>
       </c>
       <c r="B36" t="n">
-        <v>93100</v>
+        <v>93113</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4422,7 +4422,7 @@
         <v>137153568</v>
       </c>
       <c r="B37" t="n">
-        <v>93100</v>
+        <v>93113</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4524,7 +4524,7 @@
         <v>137153569</v>
       </c>
       <c r="B38" t="n">
-        <v>93100</v>
+        <v>93113</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4626,7 +4626,7 @@
         <v>137153570</v>
       </c>
       <c r="B39" t="n">
-        <v>93100</v>
+        <v>93113</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4728,7 +4728,7 @@
         <v>137153581</v>
       </c>
       <c r="B40" t="n">
-        <v>93100</v>
+        <v>93113</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4830,7 +4830,7 @@
         <v>137153582</v>
       </c>
       <c r="B41" t="n">
-        <v>93100</v>
+        <v>93113</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4932,7 +4932,7 @@
         <v>137153584</v>
       </c>
       <c r="B42" t="n">
-        <v>93100</v>
+        <v>93113</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5506,7 +5506,7 @@
         <v>137153585</v>
       </c>
       <c r="B47" t="n">
-        <v>93159</v>
+        <v>93172</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6794,7 +6794,7 @@
         <v>136707427</v>
       </c>
       <c r="B58" t="n">
-        <v>107886</v>
+        <v>107899</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7916,7 +7916,7 @@
         <v>137153566</v>
       </c>
       <c r="B69" t="n">
-        <v>111674</v>
+        <v>111687</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8018,7 +8018,7 @@
         <v>137153583</v>
       </c>
       <c r="B70" t="n">
-        <v>111674</v>
+        <v>111687</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8227,7 +8227,7 @@
         <v>136707423</v>
       </c>
       <c r="B72" t="n">
-        <v>106429</v>
+        <v>106442</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -10690,7 +10690,7 @@
         <v>137153562</v>
       </c>
       <c r="B96" t="n">
-        <v>101488</v>
+        <v>101501</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>

--- a/artfynd/A 26678-2026 artfynd.xlsx
+++ b/artfynd/A 26678-2026 artfynd.xlsx
@@ -2322,7 +2322,7 @@
         <v>136707418</v>
       </c>
       <c r="B17" t="n">
-        <v>96703</v>
+        <v>96705</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2934,7 +2934,7 @@
         <v>136707412</v>
       </c>
       <c r="B23" t="n">
-        <v>96692</v>
+        <v>96694</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -4218,7 +4218,7 @@
         <v>137153563</v>
       </c>
       <c r="B35" t="n">
-        <v>93113</v>
+        <v>93115</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4320,7 +4320,7 @@
         <v>137153564</v>
       </c>
       <c r="B36" t="n">
-        <v>93113</v>
+        <v>93115</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4422,7 +4422,7 @@
         <v>137153568</v>
       </c>
       <c r="B37" t="n">
-        <v>93113</v>
+        <v>93115</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4524,7 +4524,7 @@
         <v>137153569</v>
       </c>
       <c r="B38" t="n">
-        <v>93113</v>
+        <v>93115</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4626,7 +4626,7 @@
         <v>137153570</v>
       </c>
       <c r="B39" t="n">
-        <v>93113</v>
+        <v>93115</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4728,7 +4728,7 @@
         <v>137153581</v>
       </c>
       <c r="B40" t="n">
-        <v>93113</v>
+        <v>93115</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4830,7 +4830,7 @@
         <v>137153582</v>
       </c>
       <c r="B41" t="n">
-        <v>93113</v>
+        <v>93115</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4932,7 +4932,7 @@
         <v>137153584</v>
       </c>
       <c r="B42" t="n">
-        <v>93113</v>
+        <v>93115</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5506,7 +5506,7 @@
         <v>137153585</v>
       </c>
       <c r="B47" t="n">
-        <v>93172</v>
+        <v>93174</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6794,7 +6794,7 @@
         <v>136707427</v>
       </c>
       <c r="B58" t="n">
-        <v>107899</v>
+        <v>107901</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7916,7 +7916,7 @@
         <v>137153566</v>
       </c>
       <c r="B69" t="n">
-        <v>111687</v>
+        <v>111689</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8018,7 +8018,7 @@
         <v>137153583</v>
       </c>
       <c r="B70" t="n">
-        <v>111687</v>
+        <v>111689</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8227,7 +8227,7 @@
         <v>136707423</v>
       </c>
       <c r="B72" t="n">
-        <v>106442</v>
+        <v>106444</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -10690,7 +10690,7 @@
         <v>137153562</v>
       </c>
       <c r="B96" t="n">
-        <v>101501</v>
+        <v>101503</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>

--- a/artfynd/A 26678-2026 artfynd.xlsx
+++ b/artfynd/A 26678-2026 artfynd.xlsx
@@ -5634,11 +5634,7 @@
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Skårdalens gamla tomt, Dls</t>
@@ -5756,11 +5752,7 @@
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Barrskogen mellan Lilla Skårsdalstjärnet och Kvarntjärnet, Dls</t>
@@ -6001,11 +5993,7 @@
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Väst om Rannebergets naturreservat, Dls</t>

--- a/artfynd/A 26678-2026 artfynd.xlsx
+++ b/artfynd/A 26678-2026 artfynd.xlsx
@@ -2322,7 +2322,7 @@
         <v>136707418</v>
       </c>
       <c r="B17" t="n">
-        <v>96705</v>
+        <v>96708</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2934,7 +2934,7 @@
         <v>136707412</v>
       </c>
       <c r="B23" t="n">
-        <v>96694</v>
+        <v>96697</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -4218,7 +4218,7 @@
         <v>137153563</v>
       </c>
       <c r="B35" t="n">
-        <v>93115</v>
+        <v>93118</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4320,7 +4320,7 @@
         <v>137153564</v>
       </c>
       <c r="B36" t="n">
-        <v>93115</v>
+        <v>93118</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4422,7 +4422,7 @@
         <v>137153568</v>
       </c>
       <c r="B37" t="n">
-        <v>93115</v>
+        <v>93118</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4524,7 +4524,7 @@
         <v>137153569</v>
       </c>
       <c r="B38" t="n">
-        <v>93115</v>
+        <v>93118</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4626,7 +4626,7 @@
         <v>137153570</v>
       </c>
       <c r="B39" t="n">
-        <v>93115</v>
+        <v>93118</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4728,7 +4728,7 @@
         <v>137153581</v>
       </c>
       <c r="B40" t="n">
-        <v>93115</v>
+        <v>93118</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4830,7 +4830,7 @@
         <v>137153582</v>
       </c>
       <c r="B41" t="n">
-        <v>93115</v>
+        <v>93118</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4932,7 +4932,7 @@
         <v>137153584</v>
       </c>
       <c r="B42" t="n">
-        <v>93115</v>
+        <v>93118</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5506,7 +5506,7 @@
         <v>137153585</v>
       </c>
       <c r="B47" t="n">
-        <v>93174</v>
+        <v>93177</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6782,7 +6782,7 @@
         <v>136707427</v>
       </c>
       <c r="B58" t="n">
-        <v>107901</v>
+        <v>107905</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7904,7 +7904,7 @@
         <v>137153566</v>
       </c>
       <c r="B69" t="n">
-        <v>111689</v>
+        <v>111695</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8006,7 +8006,7 @@
         <v>137153583</v>
       </c>
       <c r="B70" t="n">
-        <v>111689</v>
+        <v>111695</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8215,7 +8215,7 @@
         <v>136707423</v>
       </c>
       <c r="B72" t="n">
-        <v>106444</v>
+        <v>106448</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -10678,7 +10678,7 @@
         <v>137153562</v>
       </c>
       <c r="B96" t="n">
-        <v>101503</v>
+        <v>101506</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>

--- a/artfynd/A 26678-2026 artfynd.xlsx
+++ b/artfynd/A 26678-2026 artfynd.xlsx
@@ -2322,7 +2322,7 @@
         <v>136707418</v>
       </c>
       <c r="B17" t="n">
-        <v>96708</v>
+        <v>96718</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2934,7 +2934,7 @@
         <v>136707412</v>
       </c>
       <c r="B23" t="n">
-        <v>96697</v>
+        <v>96707</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -4218,7 +4218,7 @@
         <v>137153563</v>
       </c>
       <c r="B35" t="n">
-        <v>93118</v>
+        <v>93128</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4320,7 +4320,7 @@
         <v>137153564</v>
       </c>
       <c r="B36" t="n">
-        <v>93118</v>
+        <v>93128</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4422,7 +4422,7 @@
         <v>137153568</v>
       </c>
       <c r="B37" t="n">
-        <v>93118</v>
+        <v>93128</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4524,7 +4524,7 @@
         <v>137153569</v>
       </c>
       <c r="B38" t="n">
-        <v>93118</v>
+        <v>93128</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4626,7 +4626,7 @@
         <v>137153570</v>
       </c>
       <c r="B39" t="n">
-        <v>93118</v>
+        <v>93128</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4728,7 +4728,7 @@
         <v>137153581</v>
       </c>
       <c r="B40" t="n">
-        <v>93118</v>
+        <v>93128</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4830,7 +4830,7 @@
         <v>137153582</v>
       </c>
       <c r="B41" t="n">
-        <v>93118</v>
+        <v>93128</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4932,7 +4932,7 @@
         <v>137153584</v>
       </c>
       <c r="B42" t="n">
-        <v>93118</v>
+        <v>93128</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5506,7 +5506,7 @@
         <v>137153585</v>
       </c>
       <c r="B47" t="n">
-        <v>93177</v>
+        <v>93187</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5608,7 +5608,7 @@
         <v>132446023</v>
       </c>
       <c r="B48" t="n">
-        <v>4777</v>
+        <v>4783</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5726,7 +5726,7 @@
         <v>132446079</v>
       </c>
       <c r="B49" t="n">
-        <v>4777</v>
+        <v>4783</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5844,7 +5844,7 @@
         <v>132446074</v>
       </c>
       <c r="B50" t="n">
-        <v>5182</v>
+        <v>5188</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5967,7 +5967,7 @@
         <v>136097897</v>
       </c>
       <c r="B51" t="n">
-        <v>5182</v>
+        <v>5188</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6782,7 +6782,7 @@
         <v>136707427</v>
       </c>
       <c r="B58" t="n">
-        <v>107905</v>
+        <v>107926</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7904,7 +7904,7 @@
         <v>137153566</v>
       </c>
       <c r="B69" t="n">
-        <v>111695</v>
+        <v>111717</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8006,7 +8006,7 @@
         <v>137153583</v>
       </c>
       <c r="B70" t="n">
-        <v>111695</v>
+        <v>111717</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8215,7 +8215,7 @@
         <v>136707423</v>
       </c>
       <c r="B72" t="n">
-        <v>106448</v>
+        <v>106467</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -10678,7 +10678,7 @@
         <v>137153562</v>
       </c>
       <c r="B96" t="n">
-        <v>101506</v>
+        <v>101521</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>

--- a/artfynd/A 26678-2026 artfynd.xlsx
+++ b/artfynd/A 26678-2026 artfynd.xlsx
@@ -4218,7 +4218,7 @@
         <v>137153563</v>
       </c>
       <c r="B35" t="n">
-        <v>93128</v>
+        <v>93129</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4320,7 +4320,7 @@
         <v>137153564</v>
       </c>
       <c r="B36" t="n">
-        <v>93128</v>
+        <v>93129</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4422,7 +4422,7 @@
         <v>137153568</v>
       </c>
       <c r="B37" t="n">
-        <v>93128</v>
+        <v>93129</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4524,7 +4524,7 @@
         <v>137153569</v>
       </c>
       <c r="B38" t="n">
-        <v>93128</v>
+        <v>93129</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4626,7 +4626,7 @@
         <v>137153570</v>
       </c>
       <c r="B39" t="n">
-        <v>93128</v>
+        <v>93129</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4728,7 +4728,7 @@
         <v>137153581</v>
       </c>
       <c r="B40" t="n">
-        <v>93128</v>
+        <v>93129</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4830,7 +4830,7 @@
         <v>137153582</v>
       </c>
       <c r="B41" t="n">
-        <v>93128</v>
+        <v>93129</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4932,7 +4932,7 @@
         <v>137153584</v>
       </c>
       <c r="B42" t="n">
-        <v>93128</v>
+        <v>93129</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5506,7 +5506,7 @@
         <v>137153585</v>
       </c>
       <c r="B47" t="n">
-        <v>93187</v>
+        <v>93188</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -7904,7 +7904,7 @@
         <v>137153566</v>
       </c>
       <c r="B69" t="n">
-        <v>111717</v>
+        <v>111718</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8006,7 +8006,7 @@
         <v>137153583</v>
       </c>
       <c r="B70" t="n">
-        <v>111717</v>
+        <v>111718</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -10678,7 +10678,7 @@
         <v>137153562</v>
       </c>
       <c r="B96" t="n">
-        <v>101521</v>
+        <v>101522</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>

--- a/artfynd/A 26678-2026 artfynd.xlsx
+++ b/artfynd/A 26678-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ98"/>
+  <dimension ref="A1:AZ99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3645,10 +3645,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132446011</v>
+        <v>137347860</v>
       </c>
       <c r="B30" t="n">
-        <v>96533</v>
+        <v>96632</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3656,34 +3656,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2818</v>
+        <v>2813</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Janses kulle, Dls</t>
+          <t>Väst om Rannebergets naturreservat, Dls</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>348654</v>
+        <v>348751</v>
       </c>
       <c r="R30" t="n">
-        <v>6519348</v>
+        <v>6519726</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3741,13 +3741,13 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132446011</t>
+          <t>https://artportalen.se/Sighting/137347860</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132446019</v>
+        <v>132446011</v>
       </c>
       <c r="B31" t="n">
         <v>96533</v>
@@ -3782,10 +3782,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>348662</v>
+        <v>348654</v>
       </c>
       <c r="R31" t="n">
-        <v>6519330</v>
+        <v>6519348</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3829,21 +3829,6 @@
       <c r="AG31" t="b">
         <v>0</v>
       </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
@@ -3858,16 +3843,16 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132446019</t>
+          <t>https://artportalen.se/Sighting/132446011</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>136097899</v>
+        <v>132446019</v>
       </c>
       <c r="B32" t="n">
-        <v>96681</v>
+        <v>96533</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3895,14 +3880,14 @@
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Väst om Rannebergets naturreservat, Dls</t>
+          <t>Janses kulle, Dls</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>348719</v>
+        <v>348662</v>
       </c>
       <c r="R32" t="n">
-        <v>6519093</v>
+        <v>6519330</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3929,12 +3914,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3975,13 +3960,13 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136097899</t>
+          <t>https://artportalen.se/Sighting/132446019</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>136097906</v>
+        <v>136097899</v>
       </c>
       <c r="B33" t="n">
         <v>96681</v>
@@ -4016,10 +4001,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>348560</v>
+        <v>348719</v>
       </c>
       <c r="R33" t="n">
-        <v>6519339</v>
+        <v>6519093</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4092,13 +4077,13 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136097906</t>
+          <t>https://artportalen.se/Sighting/136097899</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>136097907</v>
+        <v>136097906</v>
       </c>
       <c r="B34" t="n">
         <v>96681</v>
@@ -4133,10 +4118,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>348545</v>
+        <v>348560</v>
       </c>
       <c r="R34" t="n">
-        <v>6519374</v>
+        <v>6519339</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4209,16 +4194,16 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136097907</t>
+          <t>https://artportalen.se/Sighting/136097906</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>137153563</v>
+        <v>136097907</v>
       </c>
       <c r="B35" t="n">
-        <v>93129</v>
+        <v>96681</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4226,34 +4211,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4769</v>
+        <v>2818</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Väst om Ranneberget, Dls</t>
+          <t>Väst om Rannebergets naturreservat, Dls</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>348617</v>
+        <v>348545</v>
       </c>
       <c r="R35" t="n">
-        <v>6519485</v>
+        <v>6519374</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4280,12 +4265,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4296,6 +4281,21 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
@@ -4311,13 +4311,13 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137153563</t>
+          <t>https://artportalen.se/Sighting/136097907</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>137153564</v>
+        <v>137153563</v>
       </c>
       <c r="B36" t="n">
         <v>93129</v>
@@ -4352,10 +4352,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>348585</v>
+        <v>348617</v>
       </c>
       <c r="R36" t="n">
-        <v>6519443</v>
+        <v>6519485</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4413,13 +4413,13 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137153564</t>
+          <t>https://artportalen.se/Sighting/137153563</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>137153568</v>
+        <v>137153564</v>
       </c>
       <c r="B37" t="n">
         <v>93129</v>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>348584</v>
+        <v>348585</v>
       </c>
       <c r="R37" t="n">
-        <v>6519354</v>
+        <v>6519443</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4515,13 +4515,13 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137153568</t>
+          <t>https://artportalen.se/Sighting/137153564</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>137153569</v>
+        <v>137153568</v>
       </c>
       <c r="B38" t="n">
         <v>93129</v>
@@ -4556,10 +4556,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>348594</v>
+        <v>348584</v>
       </c>
       <c r="R38" t="n">
-        <v>6519310</v>
+        <v>6519354</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4617,13 +4617,13 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137153569</t>
+          <t>https://artportalen.se/Sighting/137153568</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>137153570</v>
+        <v>137153569</v>
       </c>
       <c r="B39" t="n">
         <v>93129</v>
@@ -4658,10 +4658,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>348609</v>
+        <v>348594</v>
       </c>
       <c r="R39" t="n">
-        <v>6519301</v>
+        <v>6519310</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4719,13 +4719,13 @@
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137153570</t>
+          <t>https://artportalen.se/Sighting/137153569</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>137153581</v>
+        <v>137153570</v>
       </c>
       <c r="B40" t="n">
         <v>93129</v>
@@ -4760,10 +4760,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>348710</v>
+        <v>348609</v>
       </c>
       <c r="R40" t="n">
-        <v>6519717</v>
+        <v>6519301</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4821,13 +4821,13 @@
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137153581</t>
+          <t>https://artportalen.se/Sighting/137153570</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>137153582</v>
+        <v>137153581</v>
       </c>
       <c r="B41" t="n">
         <v>93129</v>
@@ -4862,10 +4862,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>348724</v>
+        <v>348710</v>
       </c>
       <c r="R41" t="n">
-        <v>6519710</v>
+        <v>6519717</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4923,13 +4923,13 @@
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137153582</t>
+          <t>https://artportalen.se/Sighting/137153581</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>137153584</v>
+        <v>137153582</v>
       </c>
       <c r="B42" t="n">
         <v>93129</v>
@@ -4964,10 +4964,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>348722</v>
+        <v>348724</v>
       </c>
       <c r="R42" t="n">
-        <v>6519683</v>
+        <v>6519710</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5025,16 +5025,16 @@
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137153584</t>
+          <t>https://artportalen.se/Sighting/137153582</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132446025</v>
+        <v>137153584</v>
       </c>
       <c r="B43" t="n">
-        <v>92031</v>
+        <v>93129</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5042,34 +5042,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5321</v>
+        <v>4769</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Skårdalens gamla tomt, Dls</t>
+          <t>Väst om Ranneberget, Dls</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>348701</v>
+        <v>348722</v>
       </c>
       <c r="R43" t="n">
-        <v>6519282</v>
+        <v>6519683</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5096,12 +5096,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5110,24 +5110,8 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ43" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK43" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
@@ -5143,13 +5127,13 @@
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132446025</t>
+          <t>https://artportalen.se/Sighting/137153584</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132446026</v>
+        <v>132446025</v>
       </c>
       <c r="B44" t="n">
         <v>92031</v>
@@ -5184,10 +5168,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>348708</v>
+        <v>348701</v>
       </c>
       <c r="R44" t="n">
-        <v>6519267</v>
+        <v>6519282</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5261,13 +5245,13 @@
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132446026</t>
+          <t>https://artportalen.se/Sighting/132446025</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>132446028</v>
+        <v>132446026</v>
       </c>
       <c r="B45" t="n">
         <v>92031</v>
@@ -5302,10 +5286,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>348666</v>
+        <v>348708</v>
       </c>
       <c r="R45" t="n">
-        <v>6519254</v>
+        <v>6519267</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5379,16 +5363,16 @@
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132446028</t>
+          <t>https://artportalen.se/Sighting/132446026</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>136101564</v>
+        <v>132446028</v>
       </c>
       <c r="B46" t="n">
-        <v>92168</v>
+        <v>92031</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5416,14 +5400,14 @@
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Väst om Ranneberget, Dls</t>
+          <t>Skårdalens gamla tomt, Dls</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>348774</v>
+        <v>348666</v>
       </c>
       <c r="R46" t="n">
-        <v>6519585</v>
+        <v>6519254</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5450,12 +5434,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5497,16 +5481,16 @@
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136101564</t>
+          <t>https://artportalen.se/Sighting/132446028</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>137153585</v>
+        <v>136101564</v>
       </c>
       <c r="B47" t="n">
-        <v>93188</v>
+        <v>92168</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5514,21 +5498,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5836</v>
+        <v>5321</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Guldkremla</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Russula aurea</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Pers.</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5538,10 +5522,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>348798</v>
+        <v>348774</v>
       </c>
       <c r="R47" t="n">
-        <v>6519665</v>
+        <v>6519585</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5568,12 +5552,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5582,8 +5566,24 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
@@ -5599,16 +5599,16 @@
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137153585</t>
+          <t>https://artportalen.se/Sighting/136101564</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>132446023</v>
+        <v>137153585</v>
       </c>
       <c r="B48" t="n">
-        <v>4783</v>
+        <v>93188</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5616,35 +5616,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100299</v>
+        <v>5836</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Guldkremla</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Russula aurea</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>Pers.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Skårdalens gamla tomt, Dls</t>
+          <t>Väst om Ranneberget, Dls</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>348665</v>
+        <v>348798</v>
       </c>
       <c r="R48" t="n">
-        <v>6519298</v>
+        <v>6519665</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5671,12 +5670,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5687,21 +5686,6 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ48" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK48" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO48" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
@@ -5717,13 +5701,13 @@
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132446023</t>
+          <t>https://artportalen.se/Sighting/137153585</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>132446079</v>
+        <v>132446023</v>
       </c>
       <c r="B49" t="n">
         <v>4783</v>
@@ -5755,14 +5739,14 @@
       <c r="M49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Barrskogen mellan Lilla Skårsdalstjärnet och Kvarntjärnet, Dls</t>
+          <t>Skårdalens gamla tomt, Dls</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>348740</v>
+        <v>348665</v>
       </c>
       <c r="R49" t="n">
-        <v>6519761</v>
+        <v>6519298</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5835,16 +5819,16 @@
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132446079</t>
+          <t>https://artportalen.se/Sighting/132446023</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>132446074</v>
+        <v>132446079</v>
       </c>
       <c r="B50" t="n">
-        <v>5188</v>
+        <v>4783</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5852,39 +5836,35 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100526</v>
+        <v>100299</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
       <c r="M50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Barrskogen mellan Lilla Skårsdalstjärnet och Kvarntjärnet, Dls</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>348747</v>
+        <v>348740</v>
       </c>
       <c r="R50" t="n">
-        <v>6519747</v>
+        <v>6519761</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -5925,7 +5905,6 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -5958,13 +5937,13 @@
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132446074</t>
+          <t>https://artportalen.se/Sighting/132446079</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>136097897</v>
+        <v>132446074</v>
       </c>
       <c r="B51" t="n">
         <v>5188</v>
@@ -5993,17 +5972,21 @@
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
       <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Väst om Rannebergets naturreservat, Dls</t>
+          <t>Barrskogen mellan Lilla Skårsdalstjärnet och Kvarntjärnet, Dls</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>348723</v>
+        <v>348747</v>
       </c>
       <c r="R51" t="n">
-        <v>6519121</v>
+        <v>6519747</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6030,12 +6013,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6044,6 +6027,7 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -6076,16 +6060,16 @@
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136097897</t>
+          <t>https://artportalen.se/Sighting/132446074</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>136097898</v>
+        <v>136097897</v>
       </c>
       <c r="B52" t="n">
-        <v>5202</v>
+        <v>5188</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6093,29 +6077,25 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>105930</v>
+        <v>100526</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Väst om Rannebergets naturreservat, Dls</t>
@@ -6198,13 +6178,13 @@
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136097898</t>
+          <t>https://artportalen.se/Sighting/136097897</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>136097942</v>
+        <v>136097898</v>
       </c>
       <c r="B53" t="n">
         <v>5202</v>
@@ -6244,10 +6224,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>348780</v>
+        <v>348723</v>
       </c>
       <c r="R53" t="n">
-        <v>6519577</v>
+        <v>6519121</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6320,38 +6300,38 @@
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136097942</t>
+          <t>https://artportalen.se/Sighting/136097898</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>132445999</v>
+        <v>136097942</v>
       </c>
       <c r="B54" t="n">
-        <v>8374</v>
+        <v>5202</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>106540</v>
+        <v>105930</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Svart askbastborre</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hylesinus crenatus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fabricius, 1787)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6362,14 +6342,14 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Janses kulle, Dls</t>
+          <t>Väst om Rannebergets naturreservat, Dls</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>348665</v>
+        <v>348780</v>
       </c>
       <c r="R54" t="n">
-        <v>6519431</v>
+        <v>6519577</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6396,12 +6376,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6415,17 +6395,17 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>ask</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK54" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -6442,13 +6422,13 @@
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132445999</t>
+          <t>https://artportalen.se/Sighting/136097942</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>132446029</v>
+        <v>132445999</v>
       </c>
       <c r="B55" t="n">
         <v>8374</v>
@@ -6484,14 +6464,14 @@
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Skårdalens gamla tomt, Dls</t>
+          <t>Janses kulle, Dls</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>348623</v>
+        <v>348665</v>
       </c>
       <c r="R55" t="n">
-        <v>6519241</v>
+        <v>6519431</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6564,51 +6544,56 @@
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132446029</t>
+          <t>https://artportalen.se/Sighting/132445999</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>132446075</v>
+        <v>132446029</v>
       </c>
       <c r="B56" t="n">
-        <v>8449</v>
+        <v>8374</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>106554</v>
+        <v>106540</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Svart askbastborre</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Hylesinus crenatus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Fabricius, 1787)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Barrskogen mellan Lilla Skårsdalstjärnet och Kvarntjärnet, Dls</t>
+          <t>Skårdalens gamla tomt, Dls</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>348741</v>
+        <v>348623</v>
       </c>
       <c r="R56" t="n">
-        <v>6519743</v>
+        <v>6519241</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6652,6 +6637,21 @@
       <c r="AG56" t="b">
         <v>0</v>
       </c>
+      <c r="AJ56" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK56" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO56" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
@@ -6666,16 +6666,16 @@
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132446075</t>
+          <t>https://artportalen.se/Sighting/132446029</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>136097896</v>
+        <v>132446075</v>
       </c>
       <c r="B57" t="n">
-        <v>8452</v>
+        <v>8449</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6701,21 +6701,16 @@
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Väst om Rannebergets naturreservat, Dls</t>
+          <t>Barrskogen mellan Lilla Skårsdalstjärnet och Kvarntjärnet, Dls</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>348699</v>
+        <v>348741</v>
       </c>
       <c r="R57" t="n">
-        <v>6519187</v>
+        <v>6519743</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6742,12 +6737,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6773,16 +6768,16 @@
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136097896</t>
+          <t>https://artportalen.se/Sighting/132446075</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>136707427</v>
+        <v>136097896</v>
       </c>
       <c r="B58" t="n">
-        <v>107926</v>
+        <v>8452</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6790,34 +6785,39 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>219686</v>
+        <v>106554</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vätteros</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lathraea squamaria</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Väster om Rannebergets NR, Dls</t>
+          <t>Väst om Rannebergets naturreservat, Dls</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>348620</v>
+        <v>348699</v>
       </c>
       <c r="R58" t="n">
-        <v>6519302</v>
+        <v>6519187</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6844,12 +6844,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6875,33 +6875,33 @@
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136707427</t>
+          <t>https://artportalen.se/Sighting/136097896</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>136097889</v>
+        <v>136707427</v>
       </c>
       <c r="B59" t="n">
-        <v>111644</v>
+        <v>107926</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>219711</v>
+        <v>219686</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Vätteros</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Lathraea squamaria</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -6912,14 +6912,14 @@
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Väst om Rannebergets naturreservat, Dls</t>
+          <t>Väster om Rannebergets NR, Dls</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>348824</v>
+        <v>348620</v>
       </c>
       <c r="R59" t="n">
-        <v>6519586</v>
+        <v>6519302</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -6946,12 +6946,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6977,13 +6977,13 @@
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136097889</t>
+          <t>https://artportalen.se/Sighting/136707427</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>136097891</v>
+        <v>136097889</v>
       </c>
       <c r="B60" t="n">
         <v>111644</v>
@@ -7018,10 +7018,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>348614</v>
+        <v>348824</v>
       </c>
       <c r="R60" t="n">
-        <v>6519482</v>
+        <v>6519586</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7079,13 +7079,13 @@
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136097891</t>
+          <t>https://artportalen.se/Sighting/136097889</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>136097893</v>
+        <v>136097891</v>
       </c>
       <c r="B61" t="n">
         <v>111644</v>
@@ -7120,10 +7120,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>348612</v>
+        <v>348614</v>
       </c>
       <c r="R61" t="n">
-        <v>6519392</v>
+        <v>6519482</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7181,13 +7181,13 @@
       <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136097893</t>
+          <t>https://artportalen.se/Sighting/136097891</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>136097900</v>
+        <v>136097893</v>
       </c>
       <c r="B62" t="n">
         <v>111644</v>
@@ -7222,10 +7222,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>348618</v>
+        <v>348612</v>
       </c>
       <c r="R62" t="n">
-        <v>6519260</v>
+        <v>6519392</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -7283,13 +7283,13 @@
       <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136097900</t>
+          <t>https://artportalen.se/Sighting/136097893</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>136097921</v>
+        <v>136097900</v>
       </c>
       <c r="B63" t="n">
         <v>111644</v>
@@ -7324,10 +7324,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>348587</v>
+        <v>348618</v>
       </c>
       <c r="R63" t="n">
-        <v>6519511</v>
+        <v>6519260</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -7385,13 +7385,13 @@
       <c r="AY63" t="inlineStr"/>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136097921</t>
+          <t>https://artportalen.se/Sighting/136097900</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>136097933</v>
+        <v>136097921</v>
       </c>
       <c r="B64" t="n">
         <v>111644</v>
@@ -7426,10 +7426,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>348673</v>
+        <v>348587</v>
       </c>
       <c r="R64" t="n">
-        <v>6519697</v>
+        <v>6519511</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7487,13 +7487,13 @@
       <c r="AY64" t="inlineStr"/>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136097933</t>
+          <t>https://artportalen.se/Sighting/136097921</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>136097936</v>
+        <v>136097933</v>
       </c>
       <c r="B65" t="n">
         <v>111644</v>
@@ -7528,10 +7528,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>348711</v>
+        <v>348673</v>
       </c>
       <c r="R65" t="n">
-        <v>6519665</v>
+        <v>6519697</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -7589,13 +7589,13 @@
       <c r="AY65" t="inlineStr"/>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136097936</t>
+          <t>https://artportalen.se/Sighting/136097933</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>136097939</v>
+        <v>136097936</v>
       </c>
       <c r="B66" t="n">
         <v>111644</v>
@@ -7630,10 +7630,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>348745</v>
+        <v>348711</v>
       </c>
       <c r="R66" t="n">
-        <v>6519603</v>
+        <v>6519665</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -7691,13 +7691,13 @@
       <c r="AY66" t="inlineStr"/>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136097939</t>
+          <t>https://artportalen.se/Sighting/136097936</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>136097943</v>
+        <v>136097939</v>
       </c>
       <c r="B67" t="n">
         <v>111644</v>
@@ -7732,10 +7732,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>348818</v>
+        <v>348745</v>
       </c>
       <c r="R67" t="n">
-        <v>6519588</v>
+        <v>6519603</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -7793,13 +7793,13 @@
       <c r="AY67" t="inlineStr"/>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136097943</t>
+          <t>https://artportalen.se/Sighting/136097939</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>136097946</v>
+        <v>136097943</v>
       </c>
       <c r="B68" t="n">
         <v>111644</v>
@@ -7834,10 +7834,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>348846</v>
+        <v>348818</v>
       </c>
       <c r="R68" t="n">
-        <v>6519619</v>
+        <v>6519588</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -7895,16 +7895,16 @@
       <c r="AY68" t="inlineStr"/>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136097946</t>
+          <t>https://artportalen.se/Sighting/136097943</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>137153566</v>
+        <v>136097946</v>
       </c>
       <c r="B69" t="n">
-        <v>111718</v>
+        <v>111644</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7932,14 +7932,14 @@
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Väst om Ranneberget, Dls</t>
+          <t>Väst om Rannebergets naturreservat, Dls</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>348590</v>
+        <v>348846</v>
       </c>
       <c r="R69" t="n">
-        <v>6519442</v>
+        <v>6519619</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -7966,12 +7966,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7997,13 +7997,13 @@
       <c r="AY69" t="inlineStr"/>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137153566</t>
+          <t>https://artportalen.se/Sighting/136097946</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>137153583</v>
+        <v>137153566</v>
       </c>
       <c r="B70" t="n">
         <v>111718</v>
@@ -8038,10 +8038,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>348722</v>
+        <v>348590</v>
       </c>
       <c r="R70" t="n">
-        <v>6519700</v>
+        <v>6519442</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -8099,16 +8099,16 @@
       <c r="AY70" t="inlineStr"/>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137153583</t>
+          <t>https://artportalen.se/Sighting/137153566</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>132335133</v>
+        <v>137153583</v>
       </c>
       <c r="B71" t="n">
-        <v>101974</v>
+        <v>111718</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8116,16 +8116,16 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>220075</v>
+        <v>219711</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Gullpudra</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Chrysosplenium alternifolium</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -8136,17 +8136,17 @@
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Vandringstjärnet, ca 160 m NO om tjärnets norra ände, Dls</t>
+          <t>Väst om Ranneberget, Dls</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>348563</v>
+        <v>348722</v>
       </c>
       <c r="R71" t="n">
-        <v>6519443</v>
+        <v>6519700</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8170,12 +8170,12 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8186,53 +8186,48 @@
       </c>
       <c r="AG71" t="b">
         <v>0</v>
-      </c>
-      <c r="AI71" t="inlineStr">
-        <is>
-          <t>Sumpskog med klibbal.</t>
-        </is>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Leif Appelgren</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Leif Appelgren</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132335133</t>
+          <t>https://artportalen.se/Sighting/137153583</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>136707423</v>
+        <v>132335133</v>
       </c>
       <c r="B72" t="n">
-        <v>106467</v>
+        <v>101974</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>221141</v>
+        <v>220075</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Gullpudra</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Chrysosplenium alternifolium</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -8243,17 +8238,17 @@
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Väster om Rannebergets NR, Dls</t>
+          <t>Vandringstjärnet, ca 160 m NO om tjärnets norra ände, Dls</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>348660</v>
+        <v>348563</v>
       </c>
       <c r="R72" t="n">
-        <v>6519138</v>
+        <v>6519443</v>
       </c>
       <c r="S72" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8277,12 +8272,12 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8293,31 +8288,36 @@
       </c>
       <c r="AG72" t="b">
         <v>0</v>
+      </c>
+      <c r="AI72" t="inlineStr">
+        <is>
+          <t>Sumpskog med klibbal.</t>
+        </is>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Leif Appelgren</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Leif Appelgren</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136707423</t>
+          <t>https://artportalen.se/Sighting/132335133</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>136097904</v>
+        <v>136707423</v>
       </c>
       <c r="B73" t="n">
-        <v>106487</v>
+        <v>106467</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8325,34 +8325,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>221144</v>
+        <v>221141</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Väst om Rannebergets naturreservat, Dls</t>
+          <t>Väster om Rannebergets NR, Dls</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>348602</v>
+        <v>348660</v>
       </c>
       <c r="R73" t="n">
-        <v>6519311</v>
+        <v>6519138</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -8379,12 +8379,12 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8410,38 +8410,38 @@
       <c r="AY73" t="inlineStr"/>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136097904</t>
+          <t>https://artportalen.se/Sighting/136707423</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>136097886</v>
+        <v>136097904</v>
       </c>
       <c r="B74" t="n">
-        <v>102472</v>
+        <v>106487</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>221235</v>
+        <v>221144</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8451,10 +8451,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>348812</v>
+        <v>348602</v>
       </c>
       <c r="R74" t="n">
-        <v>6519662</v>
+        <v>6519311</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -8512,13 +8512,13 @@
       <c r="AY74" t="inlineStr"/>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136097886</t>
+          <t>https://artportalen.se/Sighting/136097904</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>136097892</v>
+        <v>136097886</v>
       </c>
       <c r="B75" t="n">
         <v>102472</v>
@@ -8553,10 +8553,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>348607</v>
+        <v>348812</v>
       </c>
       <c r="R75" t="n">
-        <v>6519437</v>
+        <v>6519662</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -8614,13 +8614,13 @@
       <c r="AY75" t="inlineStr"/>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136097892</t>
+          <t>https://artportalen.se/Sighting/136097886</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>136097894</v>
+        <v>136097892</v>
       </c>
       <c r="B76" t="n">
         <v>102472</v>
@@ -8655,10 +8655,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>348605</v>
+        <v>348607</v>
       </c>
       <c r="R76" t="n">
-        <v>6519385</v>
+        <v>6519437</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -8716,13 +8716,13 @@
       <c r="AY76" t="inlineStr"/>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136097894</t>
+          <t>https://artportalen.se/Sighting/136097892</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>136097901</v>
+        <v>136097894</v>
       </c>
       <c r="B77" t="n">
         <v>102472</v>
@@ -8757,10 +8757,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>348632</v>
+        <v>348605</v>
       </c>
       <c r="R77" t="n">
-        <v>6519294</v>
+        <v>6519385</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -8818,13 +8818,13 @@
       <c r="AY77" t="inlineStr"/>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136097901</t>
+          <t>https://artportalen.se/Sighting/136097894</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>136097903</v>
+        <v>136097901</v>
       </c>
       <c r="B78" t="n">
         <v>102472</v>
@@ -8859,10 +8859,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>348624</v>
+        <v>348632</v>
       </c>
       <c r="R78" t="n">
-        <v>6519288</v>
+        <v>6519294</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -8920,13 +8920,13 @@
       <c r="AY78" t="inlineStr"/>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136097903</t>
+          <t>https://artportalen.se/Sighting/136097901</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>136097913</v>
+        <v>136097903</v>
       </c>
       <c r="B79" t="n">
         <v>102472</v>
@@ -8961,10 +8961,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>348537</v>
+        <v>348624</v>
       </c>
       <c r="R79" t="n">
-        <v>6519535</v>
+        <v>6519288</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -9022,13 +9022,13 @@
       <c r="AY79" t="inlineStr"/>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136097913</t>
+          <t>https://artportalen.se/Sighting/136097903</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>136097916</v>
+        <v>136097913</v>
       </c>
       <c r="B80" t="n">
         <v>102472</v>
@@ -9063,10 +9063,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>348527</v>
+        <v>348537</v>
       </c>
       <c r="R80" t="n">
-        <v>6519500</v>
+        <v>6519535</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -9124,13 +9124,13 @@
       <c r="AY80" t="inlineStr"/>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136097916</t>
+          <t>https://artportalen.se/Sighting/136097913</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>136098084</v>
+        <v>136097916</v>
       </c>
       <c r="B81" t="n">
         <v>102472</v>
@@ -9165,10 +9165,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>348668</v>
+        <v>348527</v>
       </c>
       <c r="R81" t="n">
-        <v>6519210</v>
+        <v>6519500</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -9226,38 +9226,38 @@
       <c r="AY81" t="inlineStr"/>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136098084</t>
+          <t>https://artportalen.se/Sighting/136097916</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>136097902</v>
+        <v>136098084</v>
       </c>
       <c r="B82" t="n">
-        <v>104356</v>
+        <v>102472</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>221987</v>
+        <v>221235</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Skogsbingel</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Mercurialis perennis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9267,10 +9267,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>348624</v>
+        <v>348668</v>
       </c>
       <c r="R82" t="n">
-        <v>6519288</v>
+        <v>6519210</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>
@@ -9328,16 +9328,16 @@
       <c r="AY82" t="inlineStr"/>
       <c r="AZ82" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136097902</t>
+          <t>https://artportalen.se/Sighting/136098084</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>121791393</v>
+        <v>136097902</v>
       </c>
       <c r="B83" t="n">
-        <v>101326</v>
+        <v>104356</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9345,47 +9345,37 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>222498</v>
+        <v>221987</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogsbingel</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Mercurialis perennis</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N83" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Janses kulle, Janses kulle, Dls</t>
+          <t>Väst om Rannebergets naturreservat, Dls</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>348597</v>
+        <v>348624</v>
       </c>
       <c r="R83" t="n">
-        <v>6519354</v>
+        <v>6519288</v>
       </c>
       <c r="S83" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9409,12 +9399,12 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2024-12-30</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2024-12-30</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9425,36 +9415,31 @@
       </c>
       <c r="AG83" t="b">
         <v>0</v>
-      </c>
-      <c r="AH83" t="inlineStr">
-        <is>
-          <t>Barr-/lövbland</t>
-        </is>
       </c>
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
       <c r="AZ83" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121791393</t>
+          <t>https://artportalen.se/Sighting/136097902</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>132446006</v>
+        <v>121791393</v>
       </c>
       <c r="B84" t="n">
-        <v>101403</v>
+        <v>101326</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9480,19 +9465,29 @@
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Janses kulle, Dls</t>
+          <t>Janses kulle, Janses kulle, Dls</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>348630</v>
+        <v>348597</v>
       </c>
       <c r="R84" t="n">
-        <v>6519376</v>
+        <v>6519354</v>
       </c>
       <c r="S84" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9516,12 +9511,12 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2024-12-30</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2024-12-30</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9532,28 +9527,33 @@
       </c>
       <c r="AG84" t="b">
         <v>0</v>
+      </c>
+      <c r="AH84" t="inlineStr">
+        <is>
+          <t>Barr-/lövbland</t>
+        </is>
       </c>
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
       <c r="AZ84" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132446006</t>
+          <t>https://artportalen.se/Sighting/121791393</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>132446030</v>
+        <v>132446006</v>
       </c>
       <c r="B85" t="n">
         <v>101403</v>
@@ -9584,14 +9584,14 @@
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Skårdalens gamla tomt, Dls</t>
+          <t>Janses kulle, Dls</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>348675</v>
+        <v>348630</v>
       </c>
       <c r="R85" t="n">
-        <v>6519199</v>
+        <v>6519376</v>
       </c>
       <c r="S85" t="n">
         <v>5</v>
@@ -9649,13 +9649,13 @@
       <c r="AY85" t="inlineStr"/>
       <c r="AZ85" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132446030</t>
+          <t>https://artportalen.se/Sighting/132446006</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>132446073</v>
+        <v>132446030</v>
       </c>
       <c r="B86" t="n">
         <v>101403</v>
@@ -9686,14 +9686,14 @@
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Skog söder om Lilla Skårsdalstjärnet, Dls</t>
+          <t>Skårdalens gamla tomt, Dls</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>348729</v>
+        <v>348675</v>
       </c>
       <c r="R86" t="n">
-        <v>6519685</v>
+        <v>6519199</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>
@@ -9751,16 +9751,16 @@
       <c r="AY86" t="inlineStr"/>
       <c r="AZ86" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132446073</t>
+          <t>https://artportalen.se/Sighting/132446030</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>136097895</v>
+        <v>132446073</v>
       </c>
       <c r="B87" t="n">
-        <v>101556</v>
+        <v>101403</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9788,14 +9788,14 @@
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Väst om Rannebergets naturreservat, Dls</t>
+          <t>Skog söder om Lilla Skårsdalstjärnet, Dls</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>348593</v>
+        <v>348729</v>
       </c>
       <c r="R87" t="n">
-        <v>6519392</v>
+        <v>6519685</v>
       </c>
       <c r="S87" t="n">
         <v>5</v>
@@ -9822,12 +9822,12 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9853,13 +9853,13 @@
       <c r="AY87" t="inlineStr"/>
       <c r="AZ87" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136097895</t>
+          <t>https://artportalen.se/Sighting/132446073</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>136097917</v>
+        <v>136097895</v>
       </c>
       <c r="B88" t="n">
         <v>101556</v>
@@ -9894,10 +9894,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>348527</v>
+        <v>348593</v>
       </c>
       <c r="R88" t="n">
-        <v>6519500</v>
+        <v>6519392</v>
       </c>
       <c r="S88" t="n">
         <v>5</v>
@@ -9955,13 +9955,13 @@
       <c r="AY88" t="inlineStr"/>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136097917</t>
+          <t>https://artportalen.se/Sighting/136097895</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>136097919</v>
+        <v>136097917</v>
       </c>
       <c r="B89" t="n">
         <v>101556</v>
@@ -9996,10 +9996,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>348541</v>
+        <v>348527</v>
       </c>
       <c r="R89" t="n">
-        <v>6519474</v>
+        <v>6519500</v>
       </c>
       <c r="S89" t="n">
         <v>5</v>
@@ -10057,13 +10057,13 @@
       <c r="AY89" t="inlineStr"/>
       <c r="AZ89" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136097919</t>
+          <t>https://artportalen.se/Sighting/136097917</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>136097920</v>
+        <v>136097919</v>
       </c>
       <c r="B90" t="n">
         <v>101556</v>
@@ -10098,10 +10098,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>348563</v>
+        <v>348541</v>
       </c>
       <c r="R90" t="n">
-        <v>6519496</v>
+        <v>6519474</v>
       </c>
       <c r="S90" t="n">
         <v>5</v>
@@ -10159,13 +10159,13 @@
       <c r="AY90" t="inlineStr"/>
       <c r="AZ90" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136097920</t>
+          <t>https://artportalen.se/Sighting/136097919</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>136097940</v>
+        <v>136097920</v>
       </c>
       <c r="B91" t="n">
         <v>101556</v>
@@ -10200,10 +10200,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>348759</v>
+        <v>348563</v>
       </c>
       <c r="R91" t="n">
-        <v>6519595</v>
+        <v>6519496</v>
       </c>
       <c r="S91" t="n">
         <v>5</v>
@@ -10261,13 +10261,13 @@
       <c r="AY91" t="inlineStr"/>
       <c r="AZ91" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136097940</t>
+          <t>https://artportalen.se/Sighting/136097920</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>136097945</v>
+        <v>136097940</v>
       </c>
       <c r="B92" t="n">
         <v>101556</v>
@@ -10302,10 +10302,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>348840</v>
+        <v>348759</v>
       </c>
       <c r="R92" t="n">
-        <v>6519584</v>
+        <v>6519595</v>
       </c>
       <c r="S92" t="n">
         <v>5</v>
@@ -10363,16 +10363,16 @@
       <c r="AY92" t="inlineStr"/>
       <c r="AZ92" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136097945</t>
+          <t>https://artportalen.se/Sighting/136097940</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>136097888</v>
+        <v>136097945</v>
       </c>
       <c r="B93" t="n">
-        <v>101458</v>
+        <v>101556</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10380,21 +10380,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>222771</v>
+        <v>222498</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10404,10 +10404,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>348854</v>
+        <v>348840</v>
       </c>
       <c r="R93" t="n">
-        <v>6519653</v>
+        <v>6519584</v>
       </c>
       <c r="S93" t="n">
         <v>5</v>
@@ -10465,13 +10465,13 @@
       <c r="AY93" t="inlineStr"/>
       <c r="AZ93" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136097888</t>
+          <t>https://artportalen.se/Sighting/136097945</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>136097935</v>
+        <v>136097888</v>
       </c>
       <c r="B94" t="n">
         <v>101458</v>
@@ -10506,10 +10506,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>348713</v>
+        <v>348854</v>
       </c>
       <c r="R94" t="n">
-        <v>6519667</v>
+        <v>6519653</v>
       </c>
       <c r="S94" t="n">
         <v>5</v>
@@ -10567,13 +10567,13 @@
       <c r="AY94" t="inlineStr"/>
       <c r="AZ94" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136097935</t>
+          <t>https://artportalen.se/Sighting/136097888</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>136097937</v>
+        <v>136097935</v>
       </c>
       <c r="B95" t="n">
         <v>101458</v>
@@ -10611,7 +10611,7 @@
         <v>348713</v>
       </c>
       <c r="R95" t="n">
-        <v>6519650</v>
+        <v>6519667</v>
       </c>
       <c r="S95" t="n">
         <v>5</v>
@@ -10669,16 +10669,16 @@
       <c r="AY95" t="inlineStr"/>
       <c r="AZ95" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136097937</t>
+          <t>https://artportalen.se/Sighting/136097935</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>137153562</v>
+        <v>136097937</v>
       </c>
       <c r="B96" t="n">
-        <v>101522</v>
+        <v>101458</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10706,14 +10706,14 @@
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Väst om Ranneberget, Dls</t>
+          <t>Väst om Rannebergets naturreservat, Dls</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>348829</v>
+        <v>348713</v>
       </c>
       <c r="R96" t="n">
-        <v>6519602</v>
+        <v>6519650</v>
       </c>
       <c r="S96" t="n">
         <v>5</v>
@@ -10740,12 +10740,12 @@
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10771,16 +10771,16 @@
       <c r="AY96" t="inlineStr"/>
       <c r="AZ96" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137153562</t>
+          <t>https://artportalen.se/Sighting/136097937</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>132446009</v>
+        <v>137153562</v>
       </c>
       <c r="B97" t="n">
-        <v>80438</v>
+        <v>101522</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10788,34 +10788,34 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>229497</v>
+        <v>222771</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Janses kulle, Dls</t>
+          <t>Väst om Ranneberget, Dls</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>348626</v>
+        <v>348829</v>
       </c>
       <c r="R97" t="n">
-        <v>6519358</v>
+        <v>6519602</v>
       </c>
       <c r="S97" t="n">
         <v>5</v>
@@ -10842,12 +10842,12 @@
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10858,21 +10858,6 @@
       </c>
       <c r="AG97" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ97" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK97" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO97" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
@@ -10888,16 +10873,16 @@
       <c r="AY97" t="inlineStr"/>
       <c r="AZ97" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132446009</t>
+          <t>https://artportalen.se/Sighting/137153562</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>132446014</v>
+        <v>132446009</v>
       </c>
       <c r="B98" t="n">
-        <v>80403</v>
+        <v>80438</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10905,21 +10890,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6003719</v>
+        <v>229497</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Traslav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Scytinium lichenoides</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) Otálora, P.M.Jørg. &amp; Wedin</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10929,10 +10914,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>348655</v>
+        <v>348626</v>
       </c>
       <c r="R98" t="n">
-        <v>6519352</v>
+        <v>6519358</v>
       </c>
       <c r="S98" t="n">
         <v>5</v>
@@ -11004,6 +10989,123 @@
       </c>
       <c r="AY98" t="inlineStr"/>
       <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132446009</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>132446014</v>
+      </c>
+      <c r="B99" t="n">
+        <v>80403</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>6003719</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Traslav</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Scytinium lichenoides</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>(L.) Otálora, P.M.Jørg. &amp; Wedin</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>Janses kulle, Dls</t>
+        </is>
+      </c>
+      <c r="Q99" t="n">
+        <v>348655</v>
+      </c>
+      <c r="R99" t="n">
+        <v>6519352</v>
+      </c>
+      <c r="S99" t="n">
+        <v>5</v>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>Mellerud</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W99" t="inlineStr">
+        <is>
+          <t>Dalskog</t>
+        </is>
+      </c>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="AD99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ99" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK99" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO99" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AT99" t="inlineStr"/>
+      <c r="AW99" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX99" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/132446014</t>
         </is>
@@ -11108,6 +11210,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 26678-2026 artfynd.xlsx
+++ b/artfynd/A 26678-2026 artfynd.xlsx
@@ -3648,7 +3648,7 @@
         <v>137347860</v>
       </c>
       <c r="B30" t="n">
-        <v>96632</v>
+        <v>96637</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4320,7 +4320,7 @@
         <v>137153563</v>
       </c>
       <c r="B36" t="n">
-        <v>93129</v>
+        <v>93132</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4422,7 +4422,7 @@
         <v>137153564</v>
       </c>
       <c r="B37" t="n">
-        <v>93129</v>
+        <v>93132</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4524,7 +4524,7 @@
         <v>137153568</v>
       </c>
       <c r="B38" t="n">
-        <v>93129</v>
+        <v>93132</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4626,7 +4626,7 @@
         <v>137153569</v>
       </c>
       <c r="B39" t="n">
-        <v>93129</v>
+        <v>93132</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4728,7 +4728,7 @@
         <v>137153570</v>
       </c>
       <c r="B40" t="n">
-        <v>93129</v>
+        <v>93132</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4830,7 +4830,7 @@
         <v>137153581</v>
       </c>
       <c r="B41" t="n">
-        <v>93129</v>
+        <v>93132</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4932,7 +4932,7 @@
         <v>137153582</v>
       </c>
       <c r="B42" t="n">
-        <v>93129</v>
+        <v>93132</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5034,7 +5034,7 @@
         <v>137153584</v>
       </c>
       <c r="B43" t="n">
-        <v>93129</v>
+        <v>93132</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5608,7 +5608,7 @@
         <v>137153585</v>
       </c>
       <c r="B48" t="n">
-        <v>93188</v>
+        <v>93191</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -8006,7 +8006,7 @@
         <v>137153566</v>
       </c>
       <c r="B70" t="n">
-        <v>111718</v>
+        <v>111723</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8108,7 +8108,7 @@
         <v>137153583</v>
       </c>
       <c r="B71" t="n">
-        <v>111718</v>
+        <v>111723</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -10780,7 +10780,7 @@
         <v>137153562</v>
       </c>
       <c r="B97" t="n">
-        <v>101522</v>
+        <v>101527</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>

--- a/artfynd/A 26678-2026 artfynd.xlsx
+++ b/artfynd/A 26678-2026 artfynd.xlsx
@@ -3648,7 +3648,7 @@
         <v>137347860</v>
       </c>
       <c r="B30" t="n">
-        <v>96637</v>
+        <v>96639</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4320,7 +4320,7 @@
         <v>137153563</v>
       </c>
       <c r="B36" t="n">
-        <v>93132</v>
+        <v>93134</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4422,7 +4422,7 @@
         <v>137153564</v>
       </c>
       <c r="B37" t="n">
-        <v>93132</v>
+        <v>93134</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4524,7 +4524,7 @@
         <v>137153568</v>
       </c>
       <c r="B38" t="n">
-        <v>93132</v>
+        <v>93134</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4626,7 +4626,7 @@
         <v>137153569</v>
       </c>
       <c r="B39" t="n">
-        <v>93132</v>
+        <v>93134</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4728,7 +4728,7 @@
         <v>137153570</v>
       </c>
       <c r="B40" t="n">
-        <v>93132</v>
+        <v>93134</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4830,7 +4830,7 @@
         <v>137153581</v>
       </c>
       <c r="B41" t="n">
-        <v>93132</v>
+        <v>93134</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4932,7 +4932,7 @@
         <v>137153582</v>
       </c>
       <c r="B42" t="n">
-        <v>93132</v>
+        <v>93134</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5034,7 +5034,7 @@
         <v>137153584</v>
       </c>
       <c r="B43" t="n">
-        <v>93132</v>
+        <v>93134</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5608,7 +5608,7 @@
         <v>137153585</v>
       </c>
       <c r="B48" t="n">
-        <v>93191</v>
+        <v>93193</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -8006,7 +8006,7 @@
         <v>137153566</v>
       </c>
       <c r="B70" t="n">
-        <v>111723</v>
+        <v>111726</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8108,7 +8108,7 @@
         <v>137153583</v>
       </c>
       <c r="B71" t="n">
-        <v>111723</v>
+        <v>111726</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -10780,7 +10780,7 @@
         <v>137153562</v>
       </c>
       <c r="B97" t="n">
-        <v>101527</v>
+        <v>101530</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>

--- a/artfynd/A 26678-2026 artfynd.xlsx
+++ b/artfynd/A 26678-2026 artfynd.xlsx
@@ -3648,7 +3648,7 @@
         <v>137347860</v>
       </c>
       <c r="B30" t="n">
-        <v>96639</v>
+        <v>96645</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4320,7 +4320,7 @@
         <v>137153563</v>
       </c>
       <c r="B36" t="n">
-        <v>93134</v>
+        <v>93140</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4422,7 +4422,7 @@
         <v>137153564</v>
       </c>
       <c r="B37" t="n">
-        <v>93134</v>
+        <v>93140</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4524,7 +4524,7 @@
         <v>137153568</v>
       </c>
       <c r="B38" t="n">
-        <v>93134</v>
+        <v>93140</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4626,7 +4626,7 @@
         <v>137153569</v>
       </c>
       <c r="B39" t="n">
-        <v>93134</v>
+        <v>93140</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4728,7 +4728,7 @@
         <v>137153570</v>
       </c>
       <c r="B40" t="n">
-        <v>93134</v>
+        <v>93140</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4830,7 +4830,7 @@
         <v>137153581</v>
       </c>
       <c r="B41" t="n">
-        <v>93134</v>
+        <v>93140</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4932,7 +4932,7 @@
         <v>137153582</v>
       </c>
       <c r="B42" t="n">
-        <v>93134</v>
+        <v>93140</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5034,7 +5034,7 @@
         <v>137153584</v>
       </c>
       <c r="B43" t="n">
-        <v>93134</v>
+        <v>93140</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5608,7 +5608,7 @@
         <v>137153585</v>
       </c>
       <c r="B48" t="n">
-        <v>93193</v>
+        <v>93199</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -8006,7 +8006,7 @@
         <v>137153566</v>
       </c>
       <c r="B70" t="n">
-        <v>111726</v>
+        <v>111732</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8108,7 +8108,7 @@
         <v>137153583</v>
       </c>
       <c r="B71" t="n">
-        <v>111726</v>
+        <v>111732</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -10780,7 +10780,7 @@
         <v>137153562</v>
       </c>
       <c r="B97" t="n">
-        <v>101530</v>
+        <v>101536</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>

--- a/artfynd/A 26678-2026 artfynd.xlsx
+++ b/artfynd/A 26678-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ99"/>
+  <dimension ref="A1:AZ100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8006,7 +8006,7 @@
         <v>137153566</v>
       </c>
       <c r="B70" t="n">
-        <v>111732</v>
+        <v>111733</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8108,7 +8108,7 @@
         <v>137153583</v>
       </c>
       <c r="B71" t="n">
-        <v>111732</v>
+        <v>111733</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -10996,32 +10996,32 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>132446014</v>
+        <v>137405184</v>
       </c>
       <c r="B99" t="n">
-        <v>80403</v>
+        <v>80656</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6003719</v>
+        <v>229504</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Traslav</t>
+          <t>Grynig filtlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Scytinium lichenoides</t>
+          <t>Peltigera collina</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) Otálora, P.M.Jørg. &amp; Wedin</t>
+          <t>(Ach.) Schrad.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11031,7 +11031,7 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>348655</v>
+        <v>348663</v>
       </c>
       <c r="R99" t="n">
         <v>6519352</v>
@@ -11078,21 +11078,6 @@
       <c r="AG99" t="b">
         <v>0</v>
       </c>
-      <c r="AJ99" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK99" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO99" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
@@ -11106,6 +11091,123 @@
       </c>
       <c r="AY99" t="inlineStr"/>
       <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137405184</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>132446014</v>
+      </c>
+      <c r="B100" t="n">
+        <v>80403</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>6003719</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Traslav</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Scytinium lichenoides</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>(L.) Otálora, P.M.Jørg. &amp; Wedin</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>Janses kulle, Dls</t>
+        </is>
+      </c>
+      <c r="Q100" t="n">
+        <v>348655</v>
+      </c>
+      <c r="R100" t="n">
+        <v>6519352</v>
+      </c>
+      <c r="S100" t="n">
+        <v>5</v>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>Mellerud</t>
+        </is>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W100" t="inlineStr">
+        <is>
+          <t>Dalskog</t>
+        </is>
+      </c>
+      <c r="Y100" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="AD100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ100" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK100" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO100" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AT100" t="inlineStr"/>
+      <c r="AW100" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX100" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/132446014</t>
         </is>
@@ -11211,6 +11313,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 26678-2026 artfynd.xlsx
+++ b/artfynd/A 26678-2026 artfynd.xlsx
@@ -3648,7 +3648,7 @@
         <v>137347860</v>
       </c>
       <c r="B30" t="n">
-        <v>96645</v>
+        <v>96657</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4320,7 +4320,7 @@
         <v>137153563</v>
       </c>
       <c r="B36" t="n">
-        <v>93140</v>
+        <v>93152</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4422,7 +4422,7 @@
         <v>137153564</v>
       </c>
       <c r="B37" t="n">
-        <v>93140</v>
+        <v>93152</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4524,7 +4524,7 @@
         <v>137153568</v>
       </c>
       <c r="B38" t="n">
-        <v>93140</v>
+        <v>93152</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4626,7 +4626,7 @@
         <v>137153569</v>
       </c>
       <c r="B39" t="n">
-        <v>93140</v>
+        <v>93152</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4728,7 +4728,7 @@
         <v>137153570</v>
       </c>
       <c r="B40" t="n">
-        <v>93140</v>
+        <v>93152</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4830,7 +4830,7 @@
         <v>137153581</v>
       </c>
       <c r="B41" t="n">
-        <v>93140</v>
+        <v>93152</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4932,7 +4932,7 @@
         <v>137153582</v>
       </c>
       <c r="B42" t="n">
-        <v>93140</v>
+        <v>93152</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5034,7 +5034,7 @@
         <v>137153584</v>
       </c>
       <c r="B43" t="n">
-        <v>93140</v>
+        <v>93152</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5608,7 +5608,7 @@
         <v>137153585</v>
       </c>
       <c r="B48" t="n">
-        <v>93199</v>
+        <v>93211</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -8006,7 +8006,7 @@
         <v>137153566</v>
       </c>
       <c r="B70" t="n">
-        <v>111733</v>
+        <v>111745</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8108,7 +8108,7 @@
         <v>137153583</v>
       </c>
       <c r="B71" t="n">
-        <v>111733</v>
+        <v>111745</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -10780,7 +10780,7 @@
         <v>137153562</v>
       </c>
       <c r="B97" t="n">
-        <v>101536</v>
+        <v>101548</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10999,7 +10999,7 @@
         <v>137405184</v>
       </c>
       <c r="B99" t="n">
-        <v>80656</v>
+        <v>80667</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>

--- a/artfynd/A 26678-2026 artfynd.xlsx
+++ b/artfynd/A 26678-2026 artfynd.xlsx
@@ -3648,7 +3648,7 @@
         <v>137347860</v>
       </c>
       <c r="B30" t="n">
-        <v>96657</v>
+        <v>96658</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4320,7 +4320,7 @@
         <v>137153563</v>
       </c>
       <c r="B36" t="n">
-        <v>93152</v>
+        <v>93153</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4422,7 +4422,7 @@
         <v>137153564</v>
       </c>
       <c r="B37" t="n">
-        <v>93152</v>
+        <v>93153</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4524,7 +4524,7 @@
         <v>137153568</v>
       </c>
       <c r="B38" t="n">
-        <v>93152</v>
+        <v>93153</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4626,7 +4626,7 @@
         <v>137153569</v>
       </c>
       <c r="B39" t="n">
-        <v>93152</v>
+        <v>93153</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4728,7 +4728,7 @@
         <v>137153570</v>
       </c>
       <c r="B40" t="n">
-        <v>93152</v>
+        <v>93153</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4830,7 +4830,7 @@
         <v>137153581</v>
       </c>
       <c r="B41" t="n">
-        <v>93152</v>
+        <v>93153</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4932,7 +4932,7 @@
         <v>137153582</v>
       </c>
       <c r="B42" t="n">
-        <v>93152</v>
+        <v>93153</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5034,7 +5034,7 @@
         <v>137153584</v>
       </c>
       <c r="B43" t="n">
-        <v>93152</v>
+        <v>93153</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5608,7 +5608,7 @@
         <v>137153585</v>
       </c>
       <c r="B48" t="n">
-        <v>93211</v>
+        <v>93212</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -8006,7 +8006,7 @@
         <v>137153566</v>
       </c>
       <c r="B70" t="n">
-        <v>111745</v>
+        <v>111746</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8108,7 +8108,7 @@
         <v>137153583</v>
       </c>
       <c r="B71" t="n">
-        <v>111745</v>
+        <v>111746</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -10780,7 +10780,7 @@
         <v>137153562</v>
       </c>
       <c r="B97" t="n">
-        <v>101548</v>
+        <v>101549</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10999,7 +10999,7 @@
         <v>137405184</v>
       </c>
       <c r="B99" t="n">
-        <v>80667</v>
+        <v>80668</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>

--- a/artfynd/A 26678-2026 artfynd.xlsx
+++ b/artfynd/A 26678-2026 artfynd.xlsx
@@ -3648,7 +3648,7 @@
         <v>137347860</v>
       </c>
       <c r="B30" t="n">
-        <v>96658</v>
+        <v>96661</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4320,7 +4320,7 @@
         <v>137153563</v>
       </c>
       <c r="B36" t="n">
-        <v>93153</v>
+        <v>93156</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4422,7 +4422,7 @@
         <v>137153564</v>
       </c>
       <c r="B37" t="n">
-        <v>93153</v>
+        <v>93156</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4524,7 +4524,7 @@
         <v>137153568</v>
       </c>
       <c r="B38" t="n">
-        <v>93153</v>
+        <v>93156</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4626,7 +4626,7 @@
         <v>137153569</v>
       </c>
       <c r="B39" t="n">
-        <v>93153</v>
+        <v>93156</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4728,7 +4728,7 @@
         <v>137153570</v>
       </c>
       <c r="B40" t="n">
-        <v>93153</v>
+        <v>93156</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4830,7 +4830,7 @@
         <v>137153581</v>
       </c>
       <c r="B41" t="n">
-        <v>93153</v>
+        <v>93156</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4932,7 +4932,7 @@
         <v>137153582</v>
       </c>
       <c r="B42" t="n">
-        <v>93153</v>
+        <v>93156</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5034,7 +5034,7 @@
         <v>137153584</v>
       </c>
       <c r="B43" t="n">
-        <v>93153</v>
+        <v>93156</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5608,7 +5608,7 @@
         <v>137153585</v>
       </c>
       <c r="B48" t="n">
-        <v>93212</v>
+        <v>93215</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -8006,7 +8006,7 @@
         <v>137153566</v>
       </c>
       <c r="B70" t="n">
-        <v>111746</v>
+        <v>111749</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8108,7 +8108,7 @@
         <v>137153583</v>
       </c>
       <c r="B71" t="n">
-        <v>111746</v>
+        <v>111749</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -10780,7 +10780,7 @@
         <v>137153562</v>
       </c>
       <c r="B97" t="n">
-        <v>101549</v>
+        <v>101552</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10999,7 +10999,7 @@
         <v>137405184</v>
       </c>
       <c r="B99" t="n">
-        <v>80668</v>
+        <v>80670</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>

--- a/artfynd/A 26678-2026 artfynd.xlsx
+++ b/artfynd/A 26678-2026 artfynd.xlsx
@@ -3648,7 +3648,7 @@
         <v>137347860</v>
       </c>
       <c r="B30" t="n">
-        <v>96661</v>
+        <v>96665</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4320,7 +4320,7 @@
         <v>137153563</v>
       </c>
       <c r="B36" t="n">
-        <v>93156</v>
+        <v>93160</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4422,7 +4422,7 @@
         <v>137153564</v>
       </c>
       <c r="B37" t="n">
-        <v>93156</v>
+        <v>93160</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4524,7 +4524,7 @@
         <v>137153568</v>
       </c>
       <c r="B38" t="n">
-        <v>93156</v>
+        <v>93160</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4626,7 +4626,7 @@
         <v>137153569</v>
       </c>
       <c r="B39" t="n">
-        <v>93156</v>
+        <v>93160</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4728,7 +4728,7 @@
         <v>137153570</v>
       </c>
       <c r="B40" t="n">
-        <v>93156</v>
+        <v>93160</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4830,7 +4830,7 @@
         <v>137153581</v>
       </c>
       <c r="B41" t="n">
-        <v>93156</v>
+        <v>93160</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4932,7 +4932,7 @@
         <v>137153582</v>
       </c>
       <c r="B42" t="n">
-        <v>93156</v>
+        <v>93160</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5034,7 +5034,7 @@
         <v>137153584</v>
       </c>
       <c r="B43" t="n">
-        <v>93156</v>
+        <v>93160</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5608,7 +5608,7 @@
         <v>137153585</v>
       </c>
       <c r="B48" t="n">
-        <v>93215</v>
+        <v>93219</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -8006,7 +8006,7 @@
         <v>137153566</v>
       </c>
       <c r="B70" t="n">
-        <v>111749</v>
+        <v>111755</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8108,7 +8108,7 @@
         <v>137153583</v>
       </c>
       <c r="B71" t="n">
-        <v>111749</v>
+        <v>111755</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -10780,7 +10780,7 @@
         <v>137153562</v>
       </c>
       <c r="B97" t="n">
-        <v>101552</v>
+        <v>101556</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10999,7 +10999,7 @@
         <v>137405184</v>
       </c>
       <c r="B99" t="n">
-        <v>80670</v>
+        <v>80674</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
